--- a/research/DHE_map/Research_Portfolio_System_Map.xlsx
+++ b/research/DHE_map/Research_Portfolio_System_Map.xlsx
@@ -2,12 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Re1cb5ec826194334"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="2" r:id="R258886cdbdda4ed7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="3" r:id="R64763cf22f4c4904"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connections" sheetId="4" r:id="R6b810a3366554503"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="5" r:id="Rdca536478c2d4832"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="6" r:id="R49b7df5ee90a4482"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rde7ff4801328486a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="2" r:id="R902a257fafa14828"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="3" r:id="R758ced4621704d11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connections" sheetId="4" r:id="Rba4b7dd171534bf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="5" r:id="R3edbcb8e15e44f9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="6" r:id="R9027ae9e20aa43a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Descriptions" sheetId="7" r:id="Rf184cbe797754fb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper Descriptions" sheetId="8" r:id="Rfb4812b7e6764ae2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Descriptions" sheetId="9" r:id="R0f5472626c744123"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36,7 +39,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="36">
+  <x:fills count="37">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -213,6 +216,11 @@
         <x:fgColor rgb="FF9B51E0"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193D2A"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -221,7 +229,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="98">
+  <x:cellXfs count="101">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -402,6 +410,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -545,7 +558,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R96f4bd43f4594889"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd5226db16f8d4bf7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1316,7 +1329,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffdef5b1c8ee4af8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d9225b0be35416a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2038,7 +2051,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5209ce3c71fc47ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re134aa60ca7441bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3946,7 +3959,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b34d8f3b08f4c06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc20bbf2cdbd94323"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7784,9 +7797,600 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f1892ff34074dbf"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R975a3f8d4c714055"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ace375938d04ccc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd22a0d01e1114303"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="100" t="str">
+        <x:v>Phase</x:v>
+      </x:c>
+      <x:c r="B1" s="100" t="str">
+        <x:v>Human-centered subtitle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>Foundation</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>How your system works for you.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="25" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Construction</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>How your reality is built and shaped.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="25" customHeight="1">
+      <x:c r="A4" t="str">
+        <x:v>Action</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>How your experience becomes your actions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="25" customHeight="1">
+      <x:c r="A5" t="str">
+        <x:v>Integration</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>How you use the experience for next time.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="100" t="str">
+        <x:v>Paper</x:v>
+      </x:c>
+      <x:c r="B1" s="100" t="str">
+        <x:v>Short question or status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>Boundary Theory</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>What changes when you change what counts as “the system”?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="25" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Containment</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Just because you felt it, did it matter?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="25" customHeight="1">
+      <x:c r="A4" t="str">
+        <x:v>EndGame</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>You saw what happened. Do you know why?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="25" customHeight="1">
+      <x:c r="A5" t="str">
+        <x:v>How Long Is a Thought?</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>How long was that thought—for you, or for me?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="25" customHeight="1">
+      <x:c r="A6" t="str">
+        <x:v>Icarus</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Is your past still controlling you, or merely explaining you?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="25" customHeight="1">
+      <x:c r="A7" t="str">
+        <x:v>Squirrel</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>You wanted to do it. So why didn’t you?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="25" customHeight="1">
+      <x:c r="A8" t="str">
+        <x:v>Time</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Knowing the clock is not obeying the clock.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="25" customHeight="1">
+      <x:c r="A9" t="str">
+        <x:v>You Are Here</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>What you experience is not everything running underneath.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="25" customHeight="1">
+      <x:c r="A10" t="str">
+        <x:v>Relevance</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>You know it. But does it matter right now?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="25" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>Push</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Were you incapable, or did the world change underneath you?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="25" customHeight="1">
+      <x:c r="A12" t="str">
+        <x:v>Pull</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Did you solve the problem or finally see the other one?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="25" customHeight="1">
+      <x:c r="A13" t="str">
+        <x:v>PhoneWalletKeys</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Are you choosing something new, or forgetting what’s old?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="25" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>FuckYourFeelings</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Your feelings are real. Maybe?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="25" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>Weight</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>You understand the words. But do they mean anything to you?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="25" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>WhatchyaDoin</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>When “I want to do this” becomes “I am doing this,” what changed?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="25" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>FutureYou</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Manuscript summary pending.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="100" t="str">
+        <x:v>System</x:v>
+      </x:c>
+      <x:c r="B1" s="100" t="str">
+        <x:v>Human-centered description</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>Basal ganglia / striatum</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>Helps turn wanting into doing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="25" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Hippocampus / medial temporal lobe</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Uses lived moments to shape what comes next.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="25" customHeight="1">
+      <x:c r="A4" t="str">
+        <x:v>dACC / midcingulate cortex</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Helps detect when effort, pain, or conflict demands attention.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="25" customHeight="1">
+      <x:c r="A5" t="str">
+        <x:v>Anterior insula</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Helps your body's internal signals get noticed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="25" customHeight="1">
+      <x:c r="A6" t="str">
+        <x:v>aPFC / frontopolar cortex</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Helps you see possibilities beyond what's happening now.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="25" customHeight="1">
+      <x:c r="A7" t="str">
+        <x:v>SMA / pre-SMA</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Helps prepare your body to begin an action.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="25" customHeight="1">
+      <x:c r="A8" t="str">
+        <x:v>Valuation systems</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Helps determine what feels worth pursuing or avoiding.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="25" customHeight="1">
+      <x:c r="A9" t="str">
+        <x:v>DLPFC</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Helps you stay focused and on task.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="25" customHeight="1">
+      <x:c r="A10" t="str">
+        <x:v>Interoceptive systems</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Lets you feel what's happening inside your body.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="25" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>Posterior parietal cortex</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Helps you navigate your surroundings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="25" customHeight="1">
+      <x:c r="A12" t="str">
+        <x:v>Autonomic / arousal systems</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Adjusts how ready your body is to respond.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="25" customHeight="1">
+      <x:c r="A13" t="str">
+        <x:v>Default mode network</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Helps connect your past, identity, and imagined future.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="25" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>Frontoparietal control network</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Helps keep your attention on what you're trying to accomplish.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="25" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>Prefrontal cortex, general</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Helps you think ahead and change course when needed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="25" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>Sensory cortex / sensory systems</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Helps turn sights, sounds, and touch into experience.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="25" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>Thalamus</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Helps route information your brain needs to process.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="25" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>vmPFC / OFC</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Helps weigh what feels rewarding, risky, or worthwhile.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="25" customHeight="1">
+      <x:c r="A19" t="str">
+        <x:v>Cerebellum</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Helps movement, timing, and expectations work together smoothly.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="25" customHeight="1">
+      <x:c r="A20" t="str">
+        <x:v>Medial prefrontal cortex</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Helps connect experiences to what matters to you.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="25" customHeight="1">
+      <x:c r="A21" t="str">
+        <x:v>Posterior / mid insula</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Helps register changes happening inside your body.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="25" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>Premotor cortex</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Helps prepare how you'll move next.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="25" customHeight="1">
+      <x:c r="A23" t="str">
+        <x:v>ACC</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Helps you respond when something needs attention or effort.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="25" customHeight="1">
+      <x:c r="A24" t="str">
+        <x:v>Dorsal premotor cortex</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>Helps prepare movements based on what you're seeing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="25" customHeight="1">
+      <x:c r="A25" t="str">
+        <x:v>Frontoparietal attention network</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>Helps direct attention toward what's important right now.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="25" customHeight="1">
+      <x:c r="A26" t="str">
+        <x:v>Neuromodulatory systems</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>Changes how alert, motivated, or responsive you can become.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="25" customHeight="1">
+      <x:c r="A27" t="str">
+        <x:v>Prospective-memory / timing systems</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Helps you remember to do things when needed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="25" customHeight="1">
+      <x:c r="A28" t="str">
+        <x:v>TPJ / pSTS</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>Helps you make sense of what other people do.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="25" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>Amygdala</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Helps emotionally important things stand out.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="25" customHeight="1">
+      <x:c r="A30" t="str">
+        <x:v>Angular gyrus</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Helps you make sense of what you experience.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="25" customHeight="1">
+      <x:c r="A31" t="str">
+        <x:v>Apical dendrites</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Helps neurons combine incoming signals with wider context.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="25" customHeight="1">
+      <x:c r="A32" t="str">
+        <x:v>Association cortex</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Helps connect what you sense with what you know.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="25" customHeight="1">
+      <x:c r="A33" t="str">
+        <x:v>Brainstem</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>Keeps basic life functions going and supports alertness.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="25" customHeight="1">
+      <x:c r="A34" t="str">
+        <x:v>Cardiac systems</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>Lets your heartbeat influence how your body feels.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="25" customHeight="1">
+      <x:c r="A35" t="str">
+        <x:v>Caudate</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>Helps familiar goals guide what you choose next.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="25" customHeight="1">
+      <x:c r="A36" t="str">
+        <x:v>Frontostriatal systems</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>Helps you start, stop, or switch what you're doing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="25" customHeight="1">
+      <x:c r="A37" t="str">
+        <x:v>Gene-regulatory / plasticity systems</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>Helps experiences change how your system responds later.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="25" customHeight="1">
+      <x:c r="A38" t="str">
+        <x:v>Higher-order thalamus</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>Helps brain regions share information and coordinate activity.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="25" customHeight="1">
+      <x:c r="A39" t="str">
+        <x:v>Hypothalamus</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Helps translate bodily needs into physical responses.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="25" customHeight="1">
+      <x:c r="A40" t="str">
+        <x:v>Lateral / anterior prefrontal cortex</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Helps you reconsider options when the obvious answer fails.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="25" customHeight="1">
+      <x:c r="A41" t="str">
+        <x:v>Layer-5 pyramidal neurons</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>Helps carry brain signals toward action and bodily responses.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="25" customHeight="1">
+      <x:c r="A42" t="str">
+        <x:v>Locus coeruleus / noradrenergic system</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>Helps you become alert when something important changes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="25" customHeight="1">
+      <x:c r="A43" t="str">
+        <x:v>Motor cortex</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Helps your body carry out intended movements.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="25" customHeight="1">
+      <x:c r="A44" t="str">
+        <x:v>PCC / precuneus</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Helps connect memories and perspective with your sense of self.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="25" customHeight="1">
+      <x:c r="A45" t="str">
+        <x:v>Substantia nigra dopaminergic system</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Helps movement become more likely and gain momentum.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="25" customHeight="1">
+      <x:c r="A46" t="str">
+        <x:v>Thalamocortical circuits</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>Helps brain regions exchange signals as experience unfolds.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="25" customHeight="1">
+      <x:c r="A47" t="str">
+        <x:v>Ventral striatum</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>Helps make possible rewards feel worth pursuing.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/research/DHE_map/Research_Portfolio_System_Map.xlsx
+++ b/research/DHE_map/Research_Portfolio_System_Map.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rde7ff4801328486a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="2" r:id="R902a257fafa14828"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="3" r:id="R758ced4621704d11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connections" sheetId="4" r:id="Rba4b7dd171534bf8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="5" r:id="R3edbcb8e15e44f9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="6" r:id="R9027ae9e20aa43a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Descriptions" sheetId="7" r:id="Rf184cbe797754fb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper Descriptions" sheetId="8" r:id="Rfb4812b7e6764ae2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Descriptions" sheetId="9" r:id="R0f5472626c744123"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rbfa54650f9f443c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papers" sheetId="2" r:id="Rc3014726410d447d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Systems" sheetId="3" r:id="R85dbaee4bd0848d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connections" sheetId="4" r:id="R07fbcaf9f7c34c01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="5" r:id="R356b5cec3e6d44ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="6" r:id="R77991f79747c4a78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Descriptions" sheetId="7" r:id="R30678ac496b9477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper Descriptions" sheetId="8" r:id="R4f36f0ab400f419f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Descriptions" sheetId="9" r:id="Rf803e3ea101c46ea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -558,7 +558,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd5226db16f8d4bf7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R863d666fadd04055"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -869,8 +869,7 @@
         <x:v>Foundation papers</x:v>
       </x:c>
       <x:c r="B5" t="n">
-        <x:f>COUNTIF(Papers!B2:B200,"Foundation")</x:f>
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="88" t="str">
         <x:v>Construction</x:v>
@@ -887,8 +886,7 @@
         <x:v>Construction papers</x:v>
       </x:c>
       <x:c r="B6" t="n">
-        <x:f>COUNTIF(Papers!B2:B200,"Construction")</x:f>
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D6" s="90" t="str">
         <x:v>Action</x:v>
@@ -905,7 +903,6 @@
         <x:v>Action papers</x:v>
       </x:c>
       <x:c r="B7" t="n">
-        <x:f>COUNTIF(Papers!B2:B200,"Action")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D7" s="92" t="str">
@@ -923,7 +920,6 @@
         <x:v>Integration papers</x:v>
       </x:c>
       <x:c r="B8" t="n">
-        <x:f>COUNTIF(Papers!B2:B200,"Integration")</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1052,13 +1048,12 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E2" s="86" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A2)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="86" t="str">
-        <x:v>Containment</x:v>
+        <x:v>Relevance</x:v>
       </x:c>
       <x:c r="B3" s="86" t="str">
         <x:v>Foundation</x:v>
@@ -1070,8 +1065,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E3" s="86" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A3)</x:f>
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1088,13 +1082,12 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E4" s="86" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A4)</x:f>
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="86" t="str">
-        <x:v>How Long Is a Thought?</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="B5" s="86" t="str">
         <x:v>Foundation</x:v>
@@ -1106,13 +1099,12 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E5" s="86" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A5)</x:f>
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>How Long Is a Thought?</x:v>
       </x:c>
       <x:c r="B6" s="86" t="str">
         <x:v>Foundation</x:v>
@@ -1124,13 +1116,12 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E6" s="86" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A6)</x:f>
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="86" t="str">
-        <x:v>Squirrel</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="B7" s="86" t="str">
         <x:v>Foundation</x:v>
@@ -1142,26 +1133,24 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E7" s="86" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A7)</x:f>
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="86" t="str">
-        <x:v>Time</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="B8" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="C8" s="86" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D8" s="86" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="86" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A8)</x:f>
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1169,22 +1158,21 @@
         <x:v>You Are Here</x:v>
       </x:c>
       <x:c r="B9" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="C9" s="86" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="86" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E9" s="86" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A9)</x:f>
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="88" t="str">
-        <x:v>Relevance</x:v>
+        <x:v>Squirrel</x:v>
       </x:c>
       <x:c r="B10" s="88" t="str">
         <x:v>Construction</x:v>
@@ -1196,13 +1184,12 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E10" s="88" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A10)</x:f>
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="88" t="str">
-        <x:v>Push</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="B11" s="88" t="str">
         <x:v>Construction</x:v>
@@ -1214,13 +1201,12 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E11" s="88" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A11)</x:f>
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="88" t="str">
-        <x:v>Pull</x:v>
+        <x:v>PhoneWalletKeys</x:v>
       </x:c>
       <x:c r="B12" s="88" t="str">
         <x:v>Construction</x:v>
@@ -1232,13 +1218,12 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E12" s="88" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A12)</x:f>
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="88" t="str">
-        <x:v>PhoneWalletKeys</x:v>
+        <x:v>Pull</x:v>
       </x:c>
       <x:c r="B13" s="88" t="str">
         <x:v>Construction</x:v>
@@ -1250,13 +1235,12 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E13" s="88" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A13)</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="88" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Weight</x:v>
       </x:c>
       <x:c r="B14" s="88" t="str">
         <x:v>Construction</x:v>
@@ -1268,13 +1252,12 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E14" s="88" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A14)</x:f>
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="88" t="str">
-        <x:v>Weight</x:v>
+        <x:v>Push</x:v>
       </x:c>
       <x:c r="B15" s="88" t="str">
         <x:v>Construction</x:v>
@@ -1286,8 +1269,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E15" s="88" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A15)</x:f>
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1304,7 +1286,6 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="90" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A16)</x:f>
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -1322,14 +1303,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="92" t="n">
-        <x:f>COUNTIF(Connections!$B:$B,A17)</x:f>
         <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d9225b0be35416a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R114e6e317f454c11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1363,14 +1343,13 @@
         <x:v>Basal ganglia / striatum</x:v>
       </x:c>
       <x:c r="B2" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A2)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D2" s="34" t="str">
-        <x:v>EndGame, How Long Is a Thought?, Squirrel, Time, Relevance, PhoneWalletKeys, Weight, WhatchyaDoin, FutureYou</x:v>
+        <x:v>Relevance, EndGame, How Long Is a Thought?, Time, Squirrel, PhoneWalletKeys, Weight, WhatchyaDoin, FutureYou</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1378,14 +1357,13 @@
         <x:v>Hippocampus / medial temporal lobe</x:v>
       </x:c>
       <x:c r="B3" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A3)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D3" s="34" t="str">
-        <x:v>How Long Is a Thought?, Icarus, Time, Relevance, Pull, PhoneWalletKeys, Weight, FutureYou</x:v>
+        <x:v>Relevance, How Long Is a Thought?, Time, Icarus, PhoneWalletKeys, Pull, Weight, FutureYou</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1393,14 +1371,13 @@
         <x:v>dACC / midcingulate cortex</x:v>
       </x:c>
       <x:c r="B4" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A4)</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D4" s="34" t="str">
-        <x:v>Containment, Squirrel, You Are Here, Push, Weight, WhatchyaDoin, FutureYou</x:v>
+        <x:v>Containment, You Are Here, Squirrel, Weight, Push, WhatchyaDoin, FutureYou</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1408,14 +1385,13 @@
         <x:v>Anterior insula</x:v>
       </x:c>
       <x:c r="B5" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A5)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D5" s="34" t="str">
-        <x:v>Containment, Time, You Are Here, Push, FuckYourFeelings, Weight</x:v>
+        <x:v>Containment, Time, You Are Here, FuckYourFeelings, Weight, Push</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1423,14 +1399,13 @@
         <x:v>aPFC / frontopolar cortex</x:v>
       </x:c>
       <x:c r="B6" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A6)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C6" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D6" s="34" t="str">
-        <x:v>Squirrel, You Are Here, Relevance, Push, Pull, FutureYou</x:v>
+        <x:v>Relevance, You Are Here, Squirrel, Pull, Push, FutureYou</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1438,14 +1413,13 @@
         <x:v>SMA / pre-SMA</x:v>
       </x:c>
       <x:c r="B7" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A7)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D7" s="34" t="str">
-        <x:v>EndGame, How Long Is a Thought?, Squirrel, Time, PhoneWalletKeys, WhatchyaDoin</x:v>
+        <x:v>EndGame, How Long Is a Thought?, Time, Squirrel, PhoneWalletKeys, WhatchyaDoin</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1453,14 +1427,13 @@
         <x:v>Valuation systems</x:v>
       </x:c>
       <x:c r="B8" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A8)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C8" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D8" s="34" t="str">
-        <x:v>Icarus, Squirrel, Pull, FuckYourFeelings, Weight, FutureYou</x:v>
+        <x:v>Icarus, Squirrel, FuckYourFeelings, Pull, Weight, FutureYou</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1468,14 +1441,13 @@
         <x:v>DLPFC</x:v>
       </x:c>
       <x:c r="B9" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A9)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="C9" s="70" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D9" s="34" t="str">
-        <x:v>Squirrel, You Are Here, Push, PhoneWalletKeys, FutureYou</x:v>
+        <x:v>You Are Here, Squirrel, PhoneWalletKeys, Push, FutureYou</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1483,14 +1455,13 @@
         <x:v>Interoceptive systems</x:v>
       </x:c>
       <x:c r="B10" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A10)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="C10" s="70" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D10" s="34" t="str">
-        <x:v>Containment, Icarus, Time, FuckYourFeelings, FutureYou</x:v>
+        <x:v>Containment, Time, Icarus, FuckYourFeelings, FutureYou</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1498,7 +1469,6 @@
         <x:v>Posterior parietal cortex</x:v>
       </x:c>
       <x:c r="B11" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A11)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="C11" s="70" t="str">
@@ -1513,7 +1483,6 @@
         <x:v>Autonomic / arousal systems</x:v>
       </x:c>
       <x:c r="B12" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A12)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C12" s="70" t="str">
@@ -1528,7 +1497,6 @@
         <x:v>Default mode network</x:v>
       </x:c>
       <x:c r="B13" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A13)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C13" s="70" t="str">
@@ -1543,14 +1511,13 @@
         <x:v>Frontoparietal control network</x:v>
       </x:c>
       <x:c r="B14" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A14)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C14" s="70" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D14" s="34" t="str">
-        <x:v>Containment, Squirrel, You Are Here, FutureYou</x:v>
+        <x:v>Containment, You Are Here, Squirrel, FutureYou</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1558,14 +1525,13 @@
         <x:v>Prefrontal cortex, general</x:v>
       </x:c>
       <x:c r="B15" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A15)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C15" s="70" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D15" s="34" t="str">
-        <x:v>How Long Is a Thought?, Time, Relevance, PhoneWalletKeys</x:v>
+        <x:v>Relevance, How Long Is a Thought?, Time, PhoneWalletKeys</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1573,7 +1539,6 @@
         <x:v>Sensory cortex / sensory systems</x:v>
       </x:c>
       <x:c r="B16" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A16)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C16" s="70" t="str">
@@ -1588,7 +1553,6 @@
         <x:v>Thalamus</x:v>
       </x:c>
       <x:c r="B17" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A17)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C17" s="70" t="str">
@@ -1603,7 +1567,6 @@
         <x:v>vmPFC / OFC</x:v>
       </x:c>
       <x:c r="B18" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A18)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C18" s="70" t="str">
@@ -1618,7 +1581,6 @@
         <x:v>Cerebellum</x:v>
       </x:c>
       <x:c r="B19" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A19)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C19" s="70" t="str">
@@ -1633,7 +1595,6 @@
         <x:v>Medial prefrontal cortex</x:v>
       </x:c>
       <x:c r="B20" s="71" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A20)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C20" s="71" t="str">
@@ -1648,7 +1609,6 @@
         <x:v>Posterior / mid insula</x:v>
       </x:c>
       <x:c r="B21" s="71" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A21)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C21" s="71" t="str">
@@ -1663,7 +1623,6 @@
         <x:v>Premotor cortex</x:v>
       </x:c>
       <x:c r="B22" s="71" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A22)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C22" s="71" t="str">
@@ -1678,7 +1637,6 @@
         <x:v>ACC</x:v>
       </x:c>
       <x:c r="B23" s="71" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A23)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C23" s="71" t="str">
@@ -1693,7 +1651,6 @@
         <x:v>Dorsal premotor cortex</x:v>
       </x:c>
       <x:c r="B24" s="71" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A24)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C24" s="71" t="str">
@@ -1708,7 +1665,6 @@
         <x:v>Frontoparietal attention network</x:v>
       </x:c>
       <x:c r="B25" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A25)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C25" s="72" t="str">
@@ -1723,7 +1679,6 @@
         <x:v>Neuromodulatory systems</x:v>
       </x:c>
       <x:c r="B26" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A26)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C26" s="72" t="str">
@@ -1738,14 +1693,13 @@
         <x:v>Prospective-memory / timing systems</x:v>
       </x:c>
       <x:c r="B27" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A27)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C27" s="72" t="str">
         <x:v>Low</x:v>
       </x:c>
       <x:c r="D27" s="34" t="str">
-        <x:v>How Long Is a Thought?, Relevance</x:v>
+        <x:v>Relevance, How Long Is a Thought?</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1753,7 +1707,6 @@
         <x:v>TPJ / pSTS</x:v>
       </x:c>
       <x:c r="B28" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A28)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C28" s="72" t="str">
@@ -1768,7 +1721,6 @@
         <x:v>Amygdala</x:v>
       </x:c>
       <x:c r="B29" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A29)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C29" s="72" t="str">
@@ -1783,7 +1735,6 @@
         <x:v>Angular gyrus</x:v>
       </x:c>
       <x:c r="B30" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A30)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="72" t="str">
@@ -1798,7 +1749,6 @@
         <x:v>Apical dendrites</x:v>
       </x:c>
       <x:c r="B31" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A31)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C31" s="72" t="str">
@@ -1813,7 +1763,6 @@
         <x:v>Association cortex</x:v>
       </x:c>
       <x:c r="B32" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A32)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C32" s="72" t="str">
@@ -1828,7 +1777,6 @@
         <x:v>Brainstem</x:v>
       </x:c>
       <x:c r="B33" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A33)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C33" s="72" t="str">
@@ -1843,7 +1791,6 @@
         <x:v>Cardiac systems</x:v>
       </x:c>
       <x:c r="B34" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A34)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C34" s="72" t="str">
@@ -1858,7 +1805,6 @@
         <x:v>Caudate</x:v>
       </x:c>
       <x:c r="B35" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A35)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C35" s="72" t="str">
@@ -1873,7 +1819,6 @@
         <x:v>Frontostriatal systems</x:v>
       </x:c>
       <x:c r="B36" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A36)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C36" s="72" t="str">
@@ -1888,7 +1833,6 @@
         <x:v>Gene-regulatory / plasticity systems</x:v>
       </x:c>
       <x:c r="B37" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A37)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C37" s="72" t="str">
@@ -1903,7 +1847,6 @@
         <x:v>Higher-order thalamus</x:v>
       </x:c>
       <x:c r="B38" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A38)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C38" s="72" t="str">
@@ -1918,7 +1861,6 @@
         <x:v>Hypothalamus</x:v>
       </x:c>
       <x:c r="B39" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A39)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C39" s="72" t="str">
@@ -1933,7 +1875,6 @@
         <x:v>Lateral / anterior prefrontal cortex</x:v>
       </x:c>
       <x:c r="B40" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A40)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C40" s="72" t="str">
@@ -1948,7 +1889,6 @@
         <x:v>Layer-5 pyramidal neurons</x:v>
       </x:c>
       <x:c r="B41" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A41)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C41" s="72" t="str">
@@ -1963,7 +1903,6 @@
         <x:v>Locus coeruleus / noradrenergic system</x:v>
       </x:c>
       <x:c r="B42" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A42)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C42" s="72" t="str">
@@ -1978,7 +1917,6 @@
         <x:v>Motor cortex</x:v>
       </x:c>
       <x:c r="B43" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A43)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C43" s="72" t="str">
@@ -1993,7 +1931,6 @@
         <x:v>PCC / precuneus</x:v>
       </x:c>
       <x:c r="B44" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A44)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C44" s="72" t="str">
@@ -2008,7 +1945,6 @@
         <x:v>Substantia nigra dopaminergic system</x:v>
       </x:c>
       <x:c r="B45" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A45)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C45" s="72" t="str">
@@ -2023,7 +1959,6 @@
         <x:v>Thalamocortical circuits</x:v>
       </x:c>
       <x:c r="B46" s="34" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A46)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C46" s="34" t="str">
@@ -2038,7 +1973,6 @@
         <x:v>Ventral striatum</x:v>
       </x:c>
       <x:c r="B47" s="34" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A47)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C47" s="34" t="str">
@@ -2051,7 +1985,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re134aa60ca7441bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6611dccc4564059"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2085,13 +2019,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B2" s="86" t="str">
-        <x:v>Containment</x:v>
+        <x:v>Relevance</x:v>
       </x:c>
       <x:c r="C2" s="86" t="str">
-        <x:v>Anterior insula</x:v>
+        <x:v>Hippocampus / medial temporal lobe</x:v>
       </x:c>
       <x:c r="D2" s="86" t="str">
-        <x:v>E001</x:v>
+        <x:v>E061</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2099,13 +2033,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B3" s="86" t="str">
-        <x:v>Containment</x:v>
+        <x:v>Relevance</x:v>
       </x:c>
       <x:c r="C3" s="86" t="str">
-        <x:v>Posterior / mid insula</x:v>
+        <x:v>Prefrontal cortex, general</x:v>
       </x:c>
       <x:c r="D3" s="86" t="str">
-        <x:v>E002</x:v>
+        <x:v>E062</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2113,13 +2047,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B4" s="86" t="str">
-        <x:v>Containment</x:v>
+        <x:v>Relevance</x:v>
       </x:c>
       <x:c r="C4" s="86" t="str">
-        <x:v>dACC / midcingulate cortex</x:v>
+        <x:v>aPFC / frontopolar cortex</x:v>
       </x:c>
       <x:c r="D4" s="86" t="str">
-        <x:v>E003</x:v>
+        <x:v>E063</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2127,13 +2061,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B5" s="86" t="str">
-        <x:v>Containment</x:v>
+        <x:v>Relevance</x:v>
       </x:c>
       <x:c r="C5" s="86" t="str">
-        <x:v>Autonomic / arousal systems</x:v>
+        <x:v>Basal ganglia / striatum</x:v>
       </x:c>
       <x:c r="D5" s="86" t="str">
-        <x:v>E004</x:v>
+        <x:v>E064</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2141,13 +2075,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B6" s="86" t="str">
-        <x:v>Containment</x:v>
+        <x:v>Relevance</x:v>
       </x:c>
       <x:c r="C6" s="86" t="str">
-        <x:v>Frontoparietal control network</x:v>
+        <x:v>Prospective-memory / timing systems</x:v>
       </x:c>
       <x:c r="D6" s="86" t="str">
-        <x:v>E005</x:v>
+        <x:v>E065</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2155,13 +2089,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B7" s="86" t="str">
-        <x:v>Containment</x:v>
+        <x:v>EndGame</x:v>
       </x:c>
       <x:c r="C7" s="86" t="str">
-        <x:v>Default mode network</x:v>
+        <x:v>Dorsal premotor cortex</x:v>
       </x:c>
       <x:c r="D7" s="86" t="str">
-        <x:v>E006</x:v>
+        <x:v>E010</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2169,13 +2103,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B8" s="86" t="str">
-        <x:v>Containment</x:v>
+        <x:v>EndGame</x:v>
       </x:c>
       <x:c r="C8" s="86" t="str">
-        <x:v>Thalamus</x:v>
+        <x:v>SMA / pre-SMA</x:v>
       </x:c>
       <x:c r="D8" s="86" t="str">
-        <x:v>E007</x:v>
+        <x:v>E011</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2183,13 +2117,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B9" s="86" t="str">
-        <x:v>Containment</x:v>
+        <x:v>EndGame</x:v>
       </x:c>
       <x:c r="C9" s="86" t="str">
-        <x:v>Sensory cortex / sensory systems</x:v>
+        <x:v>Motor cortex</x:v>
       </x:c>
       <x:c r="D9" s="86" t="str">
-        <x:v>E008</x:v>
+        <x:v>E012</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2197,13 +2131,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B10" s="86" t="str">
-        <x:v>Containment</x:v>
+        <x:v>EndGame</x:v>
       </x:c>
       <x:c r="C10" s="86" t="str">
-        <x:v>Interoceptive systems</x:v>
+        <x:v>Posterior parietal cortex</x:v>
       </x:c>
       <x:c r="D10" s="86" t="str">
-        <x:v>E009</x:v>
+        <x:v>E013</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2214,10 +2148,10 @@
         <x:v>EndGame</x:v>
       </x:c>
       <x:c r="C11" s="86" t="str">
-        <x:v>Dorsal premotor cortex</x:v>
+        <x:v>Basal ganglia / striatum</x:v>
       </x:c>
       <x:c r="D11" s="86" t="str">
-        <x:v>E010</x:v>
+        <x:v>E014</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2228,10 +2162,10 @@
         <x:v>EndGame</x:v>
       </x:c>
       <x:c r="C12" s="86" t="str">
-        <x:v>SMA / pre-SMA</x:v>
+        <x:v>Cerebellum</x:v>
       </x:c>
       <x:c r="D12" s="86" t="str">
-        <x:v>E011</x:v>
+        <x:v>E015</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2242,10 +2176,10 @@
         <x:v>EndGame</x:v>
       </x:c>
       <x:c r="C13" s="86" t="str">
-        <x:v>Motor cortex</x:v>
+        <x:v>Premotor cortex</x:v>
       </x:c>
       <x:c r="D13" s="86" t="str">
-        <x:v>E012</x:v>
+        <x:v>E016</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2253,13 +2187,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B14" s="86" t="str">
-        <x:v>EndGame</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="C14" s="86" t="str">
-        <x:v>Posterior parietal cortex</x:v>
+        <x:v>Anterior insula</x:v>
       </x:c>
       <x:c r="D14" s="86" t="str">
-        <x:v>E013</x:v>
+        <x:v>E001</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2267,13 +2201,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B15" s="86" t="str">
-        <x:v>EndGame</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="C15" s="86" t="str">
-        <x:v>Basal ganglia / striatum</x:v>
+        <x:v>Posterior / mid insula</x:v>
       </x:c>
       <x:c r="D15" s="86" t="str">
-        <x:v>E014</x:v>
+        <x:v>E002</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2281,13 +2215,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B16" s="86" t="str">
-        <x:v>EndGame</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="C16" s="86" t="str">
-        <x:v>Cerebellum</x:v>
+        <x:v>dACC / midcingulate cortex</x:v>
       </x:c>
       <x:c r="D16" s="86" t="str">
-        <x:v>E015</x:v>
+        <x:v>E003</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2295,13 +2229,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B17" s="86" t="str">
-        <x:v>EndGame</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="C17" s="86" t="str">
-        <x:v>Premotor cortex</x:v>
+        <x:v>Autonomic / arousal systems</x:v>
       </x:c>
       <x:c r="D17" s="86" t="str">
-        <x:v>E016</x:v>
+        <x:v>E004</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2309,13 +2243,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B18" s="86" t="str">
-        <x:v>How Long Is a Thought?</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="C18" s="86" t="str">
-        <x:v>Hippocampus / medial temporal lobe</x:v>
+        <x:v>Frontoparietal control network</x:v>
       </x:c>
       <x:c r="D18" s="86" t="str">
-        <x:v>E017</x:v>
+        <x:v>E005</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2323,13 +2257,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B19" s="86" t="str">
-        <x:v>How Long Is a Thought?</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="C19" s="86" t="str">
-        <x:v>Prefrontal cortex, general</x:v>
+        <x:v>Default mode network</x:v>
       </x:c>
       <x:c r="D19" s="86" t="str">
-        <x:v>E018</x:v>
+        <x:v>E006</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2337,13 +2271,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B20" s="86" t="str">
-        <x:v>How Long Is a Thought?</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="C20" s="86" t="str">
-        <x:v>Frontoparietal attention network</x:v>
+        <x:v>Thalamus</x:v>
       </x:c>
       <x:c r="D20" s="86" t="str">
-        <x:v>E019</x:v>
+        <x:v>E007</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2351,13 +2285,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B21" s="86" t="str">
-        <x:v>How Long Is a Thought?</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="C21" s="86" t="str">
-        <x:v>Basal ganglia / striatum</x:v>
+        <x:v>Sensory cortex / sensory systems</x:v>
       </x:c>
       <x:c r="D21" s="86" t="str">
-        <x:v>E020</x:v>
+        <x:v>E008</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2365,13 +2299,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B22" s="86" t="str">
-        <x:v>How Long Is a Thought?</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="C22" s="86" t="str">
-        <x:v>SMA / pre-SMA</x:v>
+        <x:v>Interoceptive systems</x:v>
       </x:c>
       <x:c r="D22" s="86" t="str">
-        <x:v>E021</x:v>
+        <x:v>E009</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2382,10 +2316,10 @@
         <x:v>How Long Is a Thought?</x:v>
       </x:c>
       <x:c r="C23" s="86" t="str">
-        <x:v>Cerebellum</x:v>
+        <x:v>Hippocampus / medial temporal lobe</x:v>
       </x:c>
       <x:c r="D23" s="86" t="str">
-        <x:v>E022</x:v>
+        <x:v>E017</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -2396,10 +2330,10 @@
         <x:v>How Long Is a Thought?</x:v>
       </x:c>
       <x:c r="C24" s="86" t="str">
-        <x:v>Prospective-memory / timing systems</x:v>
+        <x:v>Prefrontal cortex, general</x:v>
       </x:c>
       <x:c r="D24" s="86" t="str">
-        <x:v>E023</x:v>
+        <x:v>E018</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -2407,13 +2341,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B25" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>How Long Is a Thought?</x:v>
       </x:c>
       <x:c r="C25" s="86" t="str">
-        <x:v>Layer-5 pyramidal neurons</x:v>
+        <x:v>Frontoparietal attention network</x:v>
       </x:c>
       <x:c r="D25" s="86" t="str">
-        <x:v>E024</x:v>
+        <x:v>E019</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2421,13 +2355,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B26" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>How Long Is a Thought?</x:v>
       </x:c>
       <x:c r="C26" s="86" t="str">
-        <x:v>Apical dendrites</x:v>
+        <x:v>Basal ganglia / striatum</x:v>
       </x:c>
       <x:c r="D26" s="86" t="str">
-        <x:v>E025</x:v>
+        <x:v>E020</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2435,13 +2369,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B27" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>How Long Is a Thought?</x:v>
       </x:c>
       <x:c r="C27" s="86" t="str">
-        <x:v>Higher-order thalamus</x:v>
+        <x:v>SMA / pre-SMA</x:v>
       </x:c>
       <x:c r="D27" s="86" t="str">
-        <x:v>E026</x:v>
+        <x:v>E021</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2449,13 +2383,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B28" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>How Long Is a Thought?</x:v>
       </x:c>
       <x:c r="C28" s="86" t="str">
-        <x:v>Thalamocortical circuits</x:v>
+        <x:v>Cerebellum</x:v>
       </x:c>
       <x:c r="D28" s="86" t="str">
-        <x:v>E027</x:v>
+        <x:v>E022</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2463,13 +2397,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B29" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>How Long Is a Thought?</x:v>
       </x:c>
       <x:c r="C29" s="86" t="str">
-        <x:v>Association cortex</x:v>
+        <x:v>Prospective-memory / timing systems</x:v>
       </x:c>
       <x:c r="D29" s="86" t="str">
-        <x:v>E028</x:v>
+        <x:v>E023</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2477,13 +2411,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B30" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="C30" s="86" t="str">
-        <x:v>Sensory cortex / sensory systems</x:v>
+        <x:v>Anterior insula</x:v>
       </x:c>
       <x:c r="D30" s="86" t="str">
-        <x:v>E029</x:v>
+        <x:v>E044</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2491,13 +2425,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B31" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="C31" s="86" t="str">
-        <x:v>Hippocampus / medial temporal lobe</x:v>
+        <x:v>Posterior / mid insula</x:v>
       </x:c>
       <x:c r="D31" s="86" t="str">
-        <x:v>E030</x:v>
+        <x:v>E045</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2505,13 +2439,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B32" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="C32" s="86" t="str">
-        <x:v>Neuromodulatory systems</x:v>
+        <x:v>ACC</x:v>
       </x:c>
       <x:c r="D32" s="86" t="str">
-        <x:v>E031</x:v>
+        <x:v>E046</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -2519,13 +2453,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B33" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="C33" s="86" t="str">
-        <x:v>Valuation systems</x:v>
+        <x:v>Hippocampus / medial temporal lobe</x:v>
       </x:c>
       <x:c r="D33" s="86" t="str">
-        <x:v>E032</x:v>
+        <x:v>E047</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -2533,13 +2467,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B34" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="C34" s="86" t="str">
-        <x:v>Interoceptive systems</x:v>
+        <x:v>Prefrontal cortex, general</x:v>
       </x:c>
       <x:c r="D34" s="86" t="str">
-        <x:v>E033</x:v>
+        <x:v>E048</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2547,13 +2481,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B35" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="C35" s="86" t="str">
-        <x:v>Gene-regulatory / plasticity systems</x:v>
+        <x:v>SMA / pre-SMA</x:v>
       </x:c>
       <x:c r="D35" s="86" t="str">
-        <x:v>E034</x:v>
+        <x:v>E049</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -2561,13 +2495,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B36" s="86" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="C36" s="86" t="str">
-        <x:v>Thalamus</x:v>
+        <x:v>Basal ganglia / striatum</x:v>
       </x:c>
       <x:c r="D36" s="86" t="str">
-        <x:v>E035</x:v>
+        <x:v>E050</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -2575,13 +2509,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B37" s="86" t="str">
-        <x:v>Squirrel</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="C37" s="86" t="str">
-        <x:v>DLPFC</x:v>
+        <x:v>Cerebellum</x:v>
       </x:c>
       <x:c r="D37" s="86" t="str">
-        <x:v>E036</x:v>
+        <x:v>E051</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2589,13 +2523,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B38" s="86" t="str">
-        <x:v>Squirrel</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="C38" s="86" t="str">
-        <x:v>aPFC / frontopolar cortex</x:v>
+        <x:v>Cardiac systems</x:v>
       </x:c>
       <x:c r="D38" s="86" t="str">
-        <x:v>E037</x:v>
+        <x:v>E052</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2603,13 +2537,13 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B39" s="86" t="str">
-        <x:v>Squirrel</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="C39" s="86" t="str">
-        <x:v>vmPFC / OFC</x:v>
+        <x:v>Interoceptive systems</x:v>
       </x:c>
       <x:c r="D39" s="86" t="str">
-        <x:v>E038</x:v>
+        <x:v>E053</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2617,307 +2551,307 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="B40" s="86" t="str">
-        <x:v>Squirrel</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="C40" s="86" t="str">
-        <x:v>dACC / midcingulate cortex</x:v>
+        <x:v>Autonomic / arousal systems</x:v>
       </x:c>
       <x:c r="D40" s="86" t="str">
-        <x:v>E039</x:v>
+        <x:v>E054</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B41" s="86" t="str">
-        <x:v>Squirrel</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="C41" s="86" t="str">
-        <x:v>Basal ganglia / striatum</x:v>
+        <x:v>Layer-5 pyramidal neurons</x:v>
       </x:c>
       <x:c r="D41" s="86" t="str">
-        <x:v>E040</x:v>
+        <x:v>E024</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B42" s="86" t="str">
-        <x:v>Squirrel</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="C42" s="86" t="str">
-        <x:v>SMA / pre-SMA</x:v>
+        <x:v>Apical dendrites</x:v>
       </x:c>
       <x:c r="D42" s="86" t="str">
-        <x:v>E041</x:v>
+        <x:v>E025</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B43" s="86" t="str">
-        <x:v>Squirrel</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="C43" s="86" t="str">
-        <x:v>Frontoparietal control network</x:v>
+        <x:v>Higher-order thalamus</x:v>
       </x:c>
       <x:c r="D43" s="86" t="str">
-        <x:v>E042</x:v>
+        <x:v>E026</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B44" s="86" t="str">
-        <x:v>Squirrel</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="C44" s="86" t="str">
-        <x:v>Valuation systems</x:v>
+        <x:v>Thalamocortical circuits</x:v>
       </x:c>
       <x:c r="D44" s="86" t="str">
-        <x:v>E043</x:v>
+        <x:v>E027</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B45" s="86" t="str">
-        <x:v>Time</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="C45" s="86" t="str">
-        <x:v>Anterior insula</x:v>
+        <x:v>Association cortex</x:v>
       </x:c>
       <x:c r="D45" s="86" t="str">
-        <x:v>E044</x:v>
+        <x:v>E028</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B46" s="86" t="str">
-        <x:v>Time</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="C46" s="86" t="str">
-        <x:v>Posterior / mid insula</x:v>
+        <x:v>Sensory cortex / sensory systems</x:v>
       </x:c>
       <x:c r="D46" s="86" t="str">
-        <x:v>E045</x:v>
+        <x:v>E029</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B47" s="86" t="str">
-        <x:v>Time</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="C47" s="86" t="str">
-        <x:v>ACC</x:v>
+        <x:v>Hippocampus / medial temporal lobe</x:v>
       </x:c>
       <x:c r="D47" s="86" t="str">
-        <x:v>E046</x:v>
+        <x:v>E030</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B48" s="86" t="str">
-        <x:v>Time</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="C48" s="86" t="str">
-        <x:v>Hippocampus / medial temporal lobe</x:v>
+        <x:v>Neuromodulatory systems</x:v>
       </x:c>
       <x:c r="D48" s="86" t="str">
-        <x:v>E047</x:v>
+        <x:v>E031</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B49" s="86" t="str">
-        <x:v>Time</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="C49" s="86" t="str">
-        <x:v>Prefrontal cortex, general</x:v>
+        <x:v>Valuation systems</x:v>
       </x:c>
       <x:c r="D49" s="86" t="str">
-        <x:v>E048</x:v>
+        <x:v>E032</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B50" s="86" t="str">
-        <x:v>Time</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="C50" s="86" t="str">
-        <x:v>SMA / pre-SMA</x:v>
+        <x:v>Interoceptive systems</x:v>
       </x:c>
       <x:c r="D50" s="86" t="str">
-        <x:v>E049</x:v>
+        <x:v>E033</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B51" s="86" t="str">
-        <x:v>Time</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="C51" s="86" t="str">
-        <x:v>Basal ganglia / striatum</x:v>
+        <x:v>Gene-regulatory / plasticity systems</x:v>
       </x:c>
       <x:c r="D51" s="86" t="str">
-        <x:v>E050</x:v>
+        <x:v>E034</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B52" s="86" t="str">
-        <x:v>Time</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="C52" s="86" t="str">
-        <x:v>Cerebellum</x:v>
+        <x:v>Thalamus</x:v>
       </x:c>
       <x:c r="D52" s="86" t="str">
-        <x:v>E051</x:v>
+        <x:v>E035</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B53" s="86" t="str">
-        <x:v>Time</x:v>
+        <x:v>You Are Here</x:v>
       </x:c>
       <x:c r="C53" s="86" t="str">
-        <x:v>Cardiac systems</x:v>
+        <x:v>DLPFC</x:v>
       </x:c>
       <x:c r="D53" s="86" t="str">
-        <x:v>E052</x:v>
+        <x:v>E055</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B54" s="86" t="str">
-        <x:v>Time</x:v>
+        <x:v>You Are Here</x:v>
       </x:c>
       <x:c r="C54" s="86" t="str">
-        <x:v>Interoceptive systems</x:v>
+        <x:v>aPFC / frontopolar cortex</x:v>
       </x:c>
       <x:c r="D54" s="86" t="str">
-        <x:v>E053</x:v>
+        <x:v>E056</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B55" s="86" t="str">
-        <x:v>Time</x:v>
+        <x:v>You Are Here</x:v>
       </x:c>
       <x:c r="C55" s="86" t="str">
-        <x:v>Autonomic / arousal systems</x:v>
+        <x:v>Posterior parietal cortex</x:v>
       </x:c>
       <x:c r="D55" s="86" t="str">
-        <x:v>E054</x:v>
+        <x:v>E057</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B56" s="86" t="str">
         <x:v>You Are Here</x:v>
       </x:c>
       <x:c r="C56" s="86" t="str">
-        <x:v>DLPFC</x:v>
+        <x:v>dACC / midcingulate cortex</x:v>
       </x:c>
       <x:c r="D56" s="86" t="str">
-        <x:v>E055</x:v>
+        <x:v>E058</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B57" s="86" t="str">
         <x:v>You Are Here</x:v>
       </x:c>
       <x:c r="C57" s="86" t="str">
-        <x:v>aPFC / frontopolar cortex</x:v>
+        <x:v>Anterior insula</x:v>
       </x:c>
       <x:c r="D57" s="86" t="str">
-        <x:v>E056</x:v>
+        <x:v>E059</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B58" s="86" t="str">
         <x:v>You Are Here</x:v>
       </x:c>
       <x:c r="C58" s="86" t="str">
-        <x:v>Posterior parietal cortex</x:v>
+        <x:v>Frontoparietal control network</x:v>
       </x:c>
       <x:c r="D58" s="86" t="str">
-        <x:v>E057</x:v>
+        <x:v>E060</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B59" s="86" t="str">
-        <x:v>You Are Here</x:v>
+        <x:v>Squirrel</x:v>
       </x:c>
       <x:c r="C59" s="86" t="str">
-        <x:v>dACC / midcingulate cortex</x:v>
+        <x:v>DLPFC</x:v>
       </x:c>
       <x:c r="D59" s="86" t="str">
-        <x:v>E058</x:v>
+        <x:v>E036</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B60" s="86" t="str">
-        <x:v>You Are Here</x:v>
+        <x:v>Squirrel</x:v>
       </x:c>
       <x:c r="C60" s="86" t="str">
-        <x:v>Anterior insula</x:v>
+        <x:v>aPFC / frontopolar cortex</x:v>
       </x:c>
       <x:c r="D60" s="86" t="str">
-        <x:v>E059</x:v>
+        <x:v>E037</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="86" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Construction</x:v>
       </x:c>
       <x:c r="B61" s="86" t="str">
-        <x:v>You Are Here</x:v>
+        <x:v>Squirrel</x:v>
       </x:c>
       <x:c r="C61" s="86" t="str">
-        <x:v>Frontoparietal control network</x:v>
+        <x:v>vmPFC / OFC</x:v>
       </x:c>
       <x:c r="D61" s="86" t="str">
-        <x:v>E060</x:v>
+        <x:v>E038</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -2925,13 +2859,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B62" s="88" t="str">
-        <x:v>Relevance</x:v>
+        <x:v>Squirrel</x:v>
       </x:c>
       <x:c r="C62" s="88" t="str">
-        <x:v>Hippocampus / medial temporal lobe</x:v>
+        <x:v>dACC / midcingulate cortex</x:v>
       </x:c>
       <x:c r="D62" s="88" t="str">
-        <x:v>E061</x:v>
+        <x:v>E039</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -2939,13 +2873,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B63" s="88" t="str">
-        <x:v>Relevance</x:v>
+        <x:v>Squirrel</x:v>
       </x:c>
       <x:c r="C63" s="88" t="str">
-        <x:v>Prefrontal cortex, general</x:v>
+        <x:v>Basal ganglia / striatum</x:v>
       </x:c>
       <x:c r="D63" s="88" t="str">
-        <x:v>E062</x:v>
+        <x:v>E040</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -2953,13 +2887,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B64" s="88" t="str">
-        <x:v>Relevance</x:v>
+        <x:v>Squirrel</x:v>
       </x:c>
       <x:c r="C64" s="88" t="str">
-        <x:v>aPFC / frontopolar cortex</x:v>
+        <x:v>SMA / pre-SMA</x:v>
       </x:c>
       <x:c r="D64" s="88" t="str">
-        <x:v>E063</x:v>
+        <x:v>E041</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -2967,13 +2901,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B65" s="88" t="str">
-        <x:v>Relevance</x:v>
+        <x:v>Squirrel</x:v>
       </x:c>
       <x:c r="C65" s="88" t="str">
-        <x:v>Basal ganglia / striatum</x:v>
+        <x:v>Frontoparietal control network</x:v>
       </x:c>
       <x:c r="D65" s="88" t="str">
-        <x:v>E064</x:v>
+        <x:v>E042</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -2981,13 +2915,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B66" s="88" t="str">
-        <x:v>Relevance</x:v>
+        <x:v>Squirrel</x:v>
       </x:c>
       <x:c r="C66" s="88" t="str">
-        <x:v>Prospective-memory / timing systems</x:v>
+        <x:v>Valuation systems</x:v>
       </x:c>
       <x:c r="D66" s="88" t="str">
-        <x:v>E065</x:v>
+        <x:v>E043</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -2995,13 +2929,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B67" s="88" t="str">
-        <x:v>Push</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="C67" s="88" t="str">
-        <x:v>DLPFC</x:v>
+        <x:v>Brainstem</x:v>
       </x:c>
       <x:c r="D67" s="88" t="str">
-        <x:v>E066</x:v>
+        <x:v>E087</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -3009,13 +2943,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B68" s="88" t="str">
-        <x:v>Push</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="C68" s="88" t="str">
-        <x:v>aPFC / frontopolar cortex</x:v>
+        <x:v>Hypothalamus</x:v>
       </x:c>
       <x:c r="D68" s="88" t="str">
-        <x:v>E067</x:v>
+        <x:v>E088</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -3023,13 +2957,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B69" s="88" t="str">
-        <x:v>Push</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="C69" s="88" t="str">
-        <x:v>Posterior parietal cortex</x:v>
+        <x:v>Thalamus</x:v>
       </x:c>
       <x:c r="D69" s="88" t="str">
-        <x:v>E068</x:v>
+        <x:v>E089</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -3037,13 +2971,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B70" s="88" t="str">
-        <x:v>Push</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="C70" s="88" t="str">
-        <x:v>dACC / midcingulate cortex</x:v>
+        <x:v>Posterior / mid insula</x:v>
       </x:c>
       <x:c r="D70" s="88" t="str">
-        <x:v>E069</x:v>
+        <x:v>E090</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -3051,13 +2985,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B71" s="88" t="str">
-        <x:v>Push</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="C71" s="88" t="str">
         <x:v>Anterior insula</x:v>
       </x:c>
       <x:c r="D71" s="88" t="str">
-        <x:v>E070</x:v>
+        <x:v>E091</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -3065,13 +2999,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B72" s="88" t="str">
-        <x:v>Push</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="C72" s="88" t="str">
-        <x:v>Frontostriatal systems</x:v>
+        <x:v>ACC</x:v>
       </x:c>
       <x:c r="D72" s="88" t="str">
-        <x:v>E071</x:v>
+        <x:v>E092</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -3079,13 +3013,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B73" s="88" t="str">
-        <x:v>Pull</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="C73" s="88" t="str">
-        <x:v>Hippocampus / medial temporal lobe</x:v>
+        <x:v>Amygdala</x:v>
       </x:c>
       <x:c r="D73" s="88" t="str">
-        <x:v>E072</x:v>
+        <x:v>E093</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -3093,13 +3027,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B74" s="88" t="str">
-        <x:v>Pull</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="C74" s="88" t="str">
-        <x:v>Medial prefrontal cortex</x:v>
+        <x:v>vmPFC / OFC</x:v>
       </x:c>
       <x:c r="D74" s="88" t="str">
-        <x:v>E073</x:v>
+        <x:v>E094</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -3107,13 +3041,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B75" s="88" t="str">
-        <x:v>Pull</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="C75" s="88" t="str">
-        <x:v>PCC / precuneus</x:v>
+        <x:v>Autonomic / arousal systems</x:v>
       </x:c>
       <x:c r="D75" s="88" t="str">
-        <x:v>E074</x:v>
+        <x:v>E095</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -3121,13 +3055,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B76" s="88" t="str">
-        <x:v>Pull</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="C76" s="88" t="str">
-        <x:v>Angular gyrus</x:v>
+        <x:v>Interoceptive systems</x:v>
       </x:c>
       <x:c r="D76" s="88" t="str">
-        <x:v>E075</x:v>
+        <x:v>E096</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -3135,13 +3069,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B77" s="88" t="str">
-        <x:v>Pull</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="C77" s="88" t="str">
-        <x:v>Default mode network</x:v>
+        <x:v>Valuation systems</x:v>
       </x:c>
       <x:c r="D77" s="88" t="str">
-        <x:v>E076</x:v>
+        <x:v>E097</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -3149,13 +3083,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B78" s="88" t="str">
-        <x:v>Pull</x:v>
+        <x:v>PhoneWalletKeys</x:v>
       </x:c>
       <x:c r="C78" s="88" t="str">
-        <x:v>Lateral / anterior prefrontal cortex</x:v>
+        <x:v>Hippocampus / medial temporal lobe</x:v>
       </x:c>
       <x:c r="D78" s="88" t="str">
-        <x:v>E077</x:v>
+        <x:v>E080</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -3163,13 +3097,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B79" s="88" t="str">
-        <x:v>Pull</x:v>
+        <x:v>PhoneWalletKeys</x:v>
       </x:c>
       <x:c r="C79" s="88" t="str">
-        <x:v>aPFC / frontopolar cortex</x:v>
+        <x:v>Prefrontal cortex, general</x:v>
       </x:c>
       <x:c r="D79" s="88" t="str">
-        <x:v>E078</x:v>
+        <x:v>E081</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -3177,13 +3111,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B80" s="88" t="str">
-        <x:v>Pull</x:v>
+        <x:v>PhoneWalletKeys</x:v>
       </x:c>
       <x:c r="C80" s="88" t="str">
-        <x:v>Valuation systems</x:v>
+        <x:v>DLPFC</x:v>
       </x:c>
       <x:c r="D80" s="88" t="str">
-        <x:v>E079</x:v>
+        <x:v>E082</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -3194,10 +3128,10 @@
         <x:v>PhoneWalletKeys</x:v>
       </x:c>
       <x:c r="C81" s="88" t="str">
-        <x:v>Hippocampus / medial temporal lobe</x:v>
+        <x:v>Caudate</x:v>
       </x:c>
       <x:c r="D81" s="88" t="str">
-        <x:v>E080</x:v>
+        <x:v>E083</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -3208,10 +3142,10 @@
         <x:v>PhoneWalletKeys</x:v>
       </x:c>
       <x:c r="C82" s="88" t="str">
-        <x:v>Prefrontal cortex, general</x:v>
+        <x:v>Basal ganglia / striatum</x:v>
       </x:c>
       <x:c r="D82" s="88" t="str">
-        <x:v>E081</x:v>
+        <x:v>E084</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -3222,10 +3156,10 @@
         <x:v>PhoneWalletKeys</x:v>
       </x:c>
       <x:c r="C83" s="88" t="str">
-        <x:v>DLPFC</x:v>
+        <x:v>Premotor cortex</x:v>
       </x:c>
       <x:c r="D83" s="88" t="str">
-        <x:v>E082</x:v>
+        <x:v>E085</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -3236,10 +3170,10 @@
         <x:v>PhoneWalletKeys</x:v>
       </x:c>
       <x:c r="C84" s="88" t="str">
-        <x:v>Caudate</x:v>
+        <x:v>SMA / pre-SMA</x:v>
       </x:c>
       <x:c r="D84" s="88" t="str">
-        <x:v>E083</x:v>
+        <x:v>E086</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -3247,13 +3181,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B85" s="88" t="str">
-        <x:v>PhoneWalletKeys</x:v>
+        <x:v>Pull</x:v>
       </x:c>
       <x:c r="C85" s="88" t="str">
-        <x:v>Basal ganglia / striatum</x:v>
+        <x:v>Hippocampus / medial temporal lobe</x:v>
       </x:c>
       <x:c r="D85" s="88" t="str">
-        <x:v>E084</x:v>
+        <x:v>E072</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -3261,13 +3195,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B86" s="88" t="str">
-        <x:v>PhoneWalletKeys</x:v>
+        <x:v>Pull</x:v>
       </x:c>
       <x:c r="C86" s="88" t="str">
-        <x:v>Premotor cortex</x:v>
+        <x:v>Medial prefrontal cortex</x:v>
       </x:c>
       <x:c r="D86" s="88" t="str">
-        <x:v>E085</x:v>
+        <x:v>E073</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -3275,13 +3209,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B87" s="88" t="str">
-        <x:v>PhoneWalletKeys</x:v>
+        <x:v>Pull</x:v>
       </x:c>
       <x:c r="C87" s="88" t="str">
-        <x:v>SMA / pre-SMA</x:v>
+        <x:v>PCC / precuneus</x:v>
       </x:c>
       <x:c r="D87" s="88" t="str">
-        <x:v>E086</x:v>
+        <x:v>E074</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -3289,13 +3223,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B88" s="88" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Pull</x:v>
       </x:c>
       <x:c r="C88" s="88" t="str">
-        <x:v>Brainstem</x:v>
+        <x:v>Angular gyrus</x:v>
       </x:c>
       <x:c r="D88" s="88" t="str">
-        <x:v>E087</x:v>
+        <x:v>E075</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -3303,13 +3237,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B89" s="88" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Pull</x:v>
       </x:c>
       <x:c r="C89" s="88" t="str">
-        <x:v>Hypothalamus</x:v>
+        <x:v>Default mode network</x:v>
       </x:c>
       <x:c r="D89" s="88" t="str">
-        <x:v>E088</x:v>
+        <x:v>E076</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -3317,13 +3251,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B90" s="88" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Pull</x:v>
       </x:c>
       <x:c r="C90" s="88" t="str">
-        <x:v>Thalamus</x:v>
+        <x:v>Lateral / anterior prefrontal cortex</x:v>
       </x:c>
       <x:c r="D90" s="88" t="str">
-        <x:v>E089</x:v>
+        <x:v>E077</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -3331,13 +3265,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B91" s="88" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Pull</x:v>
       </x:c>
       <x:c r="C91" s="88" t="str">
-        <x:v>Posterior / mid insula</x:v>
+        <x:v>aPFC / frontopolar cortex</x:v>
       </x:c>
       <x:c r="D91" s="88" t="str">
-        <x:v>E090</x:v>
+        <x:v>E078</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -3345,13 +3279,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B92" s="88" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Pull</x:v>
       </x:c>
       <x:c r="C92" s="88" t="str">
-        <x:v>Anterior insula</x:v>
+        <x:v>Valuation systems</x:v>
       </x:c>
       <x:c r="D92" s="88" t="str">
-        <x:v>E091</x:v>
+        <x:v>E079</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -3359,13 +3293,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B93" s="88" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Weight</x:v>
       </x:c>
       <x:c r="C93" s="88" t="str">
-        <x:v>ACC</x:v>
+        <x:v>vmPFC / OFC</x:v>
       </x:c>
       <x:c r="D93" s="88" t="str">
-        <x:v>E092</x:v>
+        <x:v>E098</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -3373,13 +3307,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B94" s="88" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Weight</x:v>
       </x:c>
       <x:c r="C94" s="88" t="str">
-        <x:v>Amygdala</x:v>
+        <x:v>Ventral striatum</x:v>
       </x:c>
       <x:c r="D94" s="88" t="str">
-        <x:v>E093</x:v>
+        <x:v>E099</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -3387,13 +3321,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B95" s="88" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Weight</x:v>
       </x:c>
       <x:c r="C95" s="88" t="str">
-        <x:v>vmPFC / OFC</x:v>
+        <x:v>Anterior insula</x:v>
       </x:c>
       <x:c r="D95" s="88" t="str">
-        <x:v>E094</x:v>
+        <x:v>E100</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -3401,13 +3335,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B96" s="88" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Weight</x:v>
       </x:c>
       <x:c r="C96" s="88" t="str">
-        <x:v>Autonomic / arousal systems</x:v>
+        <x:v>dACC / midcingulate cortex</x:v>
       </x:c>
       <x:c r="D96" s="88" t="str">
-        <x:v>E095</x:v>
+        <x:v>E101</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -3415,13 +3349,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B97" s="88" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Weight</x:v>
       </x:c>
       <x:c r="C97" s="88" t="str">
-        <x:v>Interoceptive systems</x:v>
+        <x:v>Hippocampus / medial temporal lobe</x:v>
       </x:c>
       <x:c r="D97" s="88" t="str">
-        <x:v>E096</x:v>
+        <x:v>E102</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -3429,13 +3363,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B98" s="88" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Weight</x:v>
       </x:c>
       <x:c r="C98" s="88" t="str">
-        <x:v>Valuation systems</x:v>
+        <x:v>Default mode network</x:v>
       </x:c>
       <x:c r="D98" s="88" t="str">
-        <x:v>E097</x:v>
+        <x:v>E103</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -3446,10 +3380,10 @@
         <x:v>Weight</x:v>
       </x:c>
       <x:c r="C99" s="88" t="str">
-        <x:v>vmPFC / OFC</x:v>
+        <x:v>Medial prefrontal cortex</x:v>
       </x:c>
       <x:c r="D99" s="88" t="str">
-        <x:v>E098</x:v>
+        <x:v>E104</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -3460,10 +3394,10 @@
         <x:v>Weight</x:v>
       </x:c>
       <x:c r="C100" s="88" t="str">
-        <x:v>Ventral striatum</x:v>
+        <x:v>TPJ / pSTS</x:v>
       </x:c>
       <x:c r="D100" s="88" t="str">
-        <x:v>E099</x:v>
+        <x:v>E105</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -3474,10 +3408,10 @@
         <x:v>Weight</x:v>
       </x:c>
       <x:c r="C101" s="88" t="str">
-        <x:v>Anterior insula</x:v>
+        <x:v>Autonomic / arousal systems</x:v>
       </x:c>
       <x:c r="D101" s="88" t="str">
-        <x:v>E100</x:v>
+        <x:v>E106</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -3488,10 +3422,10 @@
         <x:v>Weight</x:v>
       </x:c>
       <x:c r="C102" s="88" t="str">
-        <x:v>dACC / midcingulate cortex</x:v>
+        <x:v>Basal ganglia / striatum</x:v>
       </x:c>
       <x:c r="D102" s="88" t="str">
-        <x:v>E101</x:v>
+        <x:v>E107</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -3502,10 +3436,10 @@
         <x:v>Weight</x:v>
       </x:c>
       <x:c r="C103" s="88" t="str">
-        <x:v>Hippocampus / medial temporal lobe</x:v>
+        <x:v>Valuation systems</x:v>
       </x:c>
       <x:c r="D103" s="88" t="str">
-        <x:v>E102</x:v>
+        <x:v>E108</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -3513,13 +3447,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B104" s="88" t="str">
-        <x:v>Weight</x:v>
+        <x:v>Push</x:v>
       </x:c>
       <x:c r="C104" s="88" t="str">
-        <x:v>Default mode network</x:v>
+        <x:v>DLPFC</x:v>
       </x:c>
       <x:c r="D104" s="88" t="str">
-        <x:v>E103</x:v>
+        <x:v>E066</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -3527,13 +3461,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B105" s="88" t="str">
-        <x:v>Weight</x:v>
+        <x:v>Push</x:v>
       </x:c>
       <x:c r="C105" s="88" t="str">
-        <x:v>Medial prefrontal cortex</x:v>
+        <x:v>aPFC / frontopolar cortex</x:v>
       </x:c>
       <x:c r="D105" s="88" t="str">
-        <x:v>E104</x:v>
+        <x:v>E067</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -3541,13 +3475,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B106" s="88" t="str">
-        <x:v>Weight</x:v>
+        <x:v>Push</x:v>
       </x:c>
       <x:c r="C106" s="88" t="str">
-        <x:v>TPJ / pSTS</x:v>
+        <x:v>Posterior parietal cortex</x:v>
       </x:c>
       <x:c r="D106" s="88" t="str">
-        <x:v>E105</x:v>
+        <x:v>E068</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -3555,13 +3489,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B107" s="88" t="str">
-        <x:v>Weight</x:v>
+        <x:v>Push</x:v>
       </x:c>
       <x:c r="C107" s="88" t="str">
-        <x:v>Autonomic / arousal systems</x:v>
+        <x:v>dACC / midcingulate cortex</x:v>
       </x:c>
       <x:c r="D107" s="88" t="str">
-        <x:v>E106</x:v>
+        <x:v>E069</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -3569,13 +3503,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B108" s="88" t="str">
-        <x:v>Weight</x:v>
+        <x:v>Push</x:v>
       </x:c>
       <x:c r="C108" s="88" t="str">
-        <x:v>Basal ganglia / striatum</x:v>
+        <x:v>Anterior insula</x:v>
       </x:c>
       <x:c r="D108" s="88" t="str">
-        <x:v>E107</x:v>
+        <x:v>E070</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -3583,13 +3517,13 @@
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="B109" s="88" t="str">
-        <x:v>Weight</x:v>
+        <x:v>Push</x:v>
       </x:c>
       <x:c r="C109" s="88" t="str">
-        <x:v>Valuation systems</x:v>
+        <x:v>Frontostriatal systems</x:v>
       </x:c>
       <x:c r="D109" s="88" t="str">
-        <x:v>E108</x:v>
+        <x:v>E071</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -3959,7 +3893,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc20bbf2cdbd94323"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R740a42d57c384042"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4169,299 +4103,116 @@
       <x:c r="B2" s="95" t="str">
         <x:v>Foundation</x:v>
       </x:c>
-      <x:c r="C2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="D2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="E2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="F2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="G2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="H2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="I2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="J2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="K2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="L2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="M2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="N2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="O2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="P2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Q2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="R2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="S2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="T2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="U2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="W2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Y2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV2" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A2,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+      <x:c r="C2" s="34"/>
+      <x:c r="D2" s="34"/>
+      <x:c r="E2" s="34"/>
+      <x:c r="F2" s="34"/>
+      <x:c r="G2" s="34"/>
+      <x:c r="H2" s="34"/>
+      <x:c r="I2" s="34"/>
+      <x:c r="J2" s="34"/>
+      <x:c r="K2" s="34"/>
+      <x:c r="L2" s="34"/>
+      <x:c r="M2" s="34"/>
+      <x:c r="N2" s="34"/>
+      <x:c r="O2" s="34"/>
+      <x:c r="P2" s="34"/>
+      <x:c r="Q2" s="34"/>
+      <x:c r="R2" s="34"/>
+      <x:c r="S2" s="34"/>
+      <x:c r="T2" s="34"/>
+      <x:c r="U2" s="34"/>
+      <x:c r="V2" s="34"/>
+      <x:c r="W2" s="34"/>
+      <x:c r="X2" s="34"/>
+      <x:c r="Y2" s="34"/>
+      <x:c r="Z2" s="34"/>
+      <x:c r="AA2" s="34"/>
+      <x:c r="AB2" s="34"/>
+      <x:c r="AC2" s="34"/>
+      <x:c r="AD2" s="34"/>
+      <x:c r="AE2" s="34"/>
+      <x:c r="AF2" s="34"/>
+      <x:c r="AG2" s="34"/>
+      <x:c r="AH2" s="34"/>
+      <x:c r="AI2" s="34"/>
+      <x:c r="AJ2" s="34"/>
+      <x:c r="AK2" s="34"/>
+      <x:c r="AL2" s="34"/>
+      <x:c r="AM2" s="34"/>
+      <x:c r="AN2" s="34"/>
+      <x:c r="AO2" s="34"/>
+      <x:c r="AP2" s="34"/>
+      <x:c r="AQ2" s="34"/>
+      <x:c r="AR2" s="34"/>
+      <x:c r="AS2" s="34"/>
+      <x:c r="AT2" s="34"/>
+      <x:c r="AU2" s="34"/>
+      <x:c r="AV2" s="34"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="95" t="str">
-        <x:v>Containment</x:v>
+        <x:v>Relevance</x:v>
       </x:c>
       <x:c r="B3" s="95" t="str">
         <x:v>Foundation</x:v>
       </x:c>
-      <x:c r="C3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="D3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="E3" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F3" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G3" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="H3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="I3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="J3" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="K3" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L3" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="M3" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N3" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P3" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Q3" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R3" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S3" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="T3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="U3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V3" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Y3" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV3" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A3,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+      <x:c r="C3" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E3" s="76"/>
+      <x:c r="F3" s="34"/>
+      <x:c r="G3" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H3" s="34"/>
+      <x:c r="I3" s="34"/>
+      <x:c r="J3" s="76"/>
+      <x:c r="K3" s="34"/>
+      <x:c r="L3" s="76"/>
+      <x:c r="M3" s="34"/>
+      <x:c r="N3" s="34"/>
+      <x:c r="O3" s="76"/>
+      <x:c r="P3" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q3" s="76"/>
+      <x:c r="R3" s="34"/>
+      <x:c r="S3" s="76"/>
+      <x:c r="T3" s="34"/>
+      <x:c r="U3" s="34"/>
+      <x:c r="V3" s="34"/>
+      <x:c r="W3" s="34"/>
+      <x:c r="X3" s="34"/>
+      <x:c r="Y3" s="76"/>
+      <x:c r="Z3" s="34"/>
+      <x:c r="AA3" s="34"/>
+      <x:c r="AB3" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC3" s="34"/>
+      <x:c r="AD3" s="34"/>
+      <x:c r="AE3" s="34"/>
+      <x:c r="AF3" s="34"/>
+      <x:c r="AG3" s="34"/>
+      <x:c r="AH3" s="34"/>
+      <x:c r="AI3" s="34"/>
+      <x:c r="AJ3" s="34"/>
+      <x:c r="AK3" s="34"/>
+      <x:c r="AL3" s="34"/>
+      <x:c r="AM3" s="34"/>
+      <x:c r="AN3" s="34"/>
+      <x:c r="AO3" s="34"/>
+      <x:c r="AP3" s="34"/>
+      <x:c r="AQ3" s="34"/>
+      <x:c r="AR3" s="34"/>
+      <x:c r="AS3" s="34"/>
+      <x:c r="AT3" s="34"/>
+      <x:c r="AU3" s="34"/>
+      <x:c r="AV3" s="34"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="95" t="str">
@@ -4471,1848 +4222,851 @@
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="C4" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="E4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="F4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="G4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4" s="34"/>
+      <x:c r="E4" s="34"/>
+      <x:c r="F4" s="34"/>
+      <x:c r="G4" s="34"/>
       <x:c r="H4" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="J4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="K4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I4" s="34"/>
+      <x:c r="J4" s="34"/>
+      <x:c r="K4" s="34"/>
       <x:c r="L4" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="N4" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="O4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="P4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Q4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="R4" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="S4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M4" s="34"/>
+      <x:c r="N4" s="76"/>
+      <x:c r="O4" s="34"/>
+      <x:c r="P4" s="34"/>
+      <x:c r="Q4" s="34"/>
+      <x:c r="R4" s="76"/>
+      <x:c r="S4" s="34"/>
       <x:c r="T4" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U4" s="34"/>
+      <x:c r="V4" s="34"/>
       <x:c r="W4" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X4" s="34"/>
       <x:c r="Y4" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG4" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO4" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z4" s="34"/>
+      <x:c r="AA4" s="34"/>
+      <x:c r="AB4" s="34"/>
+      <x:c r="AC4" s="34"/>
+      <x:c r="AD4" s="34"/>
+      <x:c r="AE4" s="34"/>
+      <x:c r="AF4" s="34"/>
+      <x:c r="AG4" s="76"/>
+      <x:c r="AH4" s="34"/>
+      <x:c r="AI4" s="34"/>
+      <x:c r="AJ4" s="34"/>
+      <x:c r="AK4" s="34"/>
+      <x:c r="AL4" s="34"/>
+      <x:c r="AM4" s="34"/>
+      <x:c r="AN4" s="34"/>
+      <x:c r="AO4" s="76"/>
+      <x:c r="AP4" s="34"/>
+      <x:c r="AQ4" s="34"/>
       <x:c r="AR4" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV4" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A4,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS4" s="34"/>
+      <x:c r="AT4" s="34"/>
+      <x:c r="AU4" s="34"/>
+      <x:c r="AV4" s="34"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="95" t="str">
-        <x:v>How Long Is a Thought?</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="B5" s="95" t="str">
         <x:v>Foundation</x:v>
       </x:c>
-      <x:c r="C5" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="F5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="G5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="H5" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="J5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="K5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="L5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="M5" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="N5" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="O5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="P5" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="R5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="S5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="T5" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="W5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X5" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Y5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z5" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB5" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH5" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV5" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A5,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+      <x:c r="C5" s="76"/>
+      <x:c r="D5" s="76"/>
+      <x:c r="E5" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G5" s="34"/>
+      <x:c r="H5" s="76"/>
+      <x:c r="I5" s="34"/>
+      <x:c r="J5" s="34"/>
+      <x:c r="K5" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L5" s="34"/>
+      <x:c r="M5" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N5" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O5" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P5" s="34"/>
+      <x:c r="Q5" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R5" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S5" s="34"/>
+      <x:c r="T5" s="34"/>
+      <x:c r="U5" s="34"/>
+      <x:c r="V5" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W5" s="34"/>
+      <x:c r="X5" s="76"/>
+      <x:c r="Y5" s="34"/>
+      <x:c r="Z5" s="34"/>
+      <x:c r="AA5" s="34"/>
+      <x:c r="AB5" s="34"/>
+      <x:c r="AC5" s="34"/>
+      <x:c r="AD5" s="34"/>
+      <x:c r="AE5" s="34"/>
+      <x:c r="AF5" s="34"/>
+      <x:c r="AG5" s="34"/>
+      <x:c r="AH5" s="76"/>
+      <x:c r="AI5" s="34"/>
+      <x:c r="AJ5" s="34"/>
+      <x:c r="AK5" s="34"/>
+      <x:c r="AL5" s="34"/>
+      <x:c r="AM5" s="34"/>
+      <x:c r="AN5" s="34"/>
+      <x:c r="AO5" s="34"/>
+      <x:c r="AP5" s="34"/>
+      <x:c r="AQ5" s="34"/>
+      <x:c r="AR5" s="34"/>
+      <x:c r="AS5" s="34"/>
+      <x:c r="AT5" s="34"/>
+      <x:c r="AU5" s="34"/>
+      <x:c r="AV5" s="34"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="95" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>How Long Is a Thought?</x:v>
       </x:c>
       <x:c r="B6" s="95" t="str">
         <x:v>Foundation</x:v>
       </x:c>
-      <x:c r="C6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
+      <x:c r="C6" s="34" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="F6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="G6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="H6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="I6" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="K6" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L6" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="M6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="N6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="O6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="P6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Q6" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R6" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S6" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="T6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="U6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="W6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Y6" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA6" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB6" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC6" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF6" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG6" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ6" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK6" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL6" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM6" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN6" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP6" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR6" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU6" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV6" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A6,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="34"/>
+      <x:c r="F6" s="34"/>
+      <x:c r="G6" s="34"/>
+      <x:c r="H6" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I6" s="76"/>
+      <x:c r="J6" s="34"/>
+      <x:c r="K6" s="34"/>
+      <x:c r="L6" s="76"/>
+      <x:c r="M6" s="34"/>
+      <x:c r="N6" s="34"/>
+      <x:c r="O6" s="34"/>
+      <x:c r="P6" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q6" s="34"/>
+      <x:c r="R6" s="34"/>
+      <x:c r="S6" s="76"/>
+      <x:c r="T6" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U6" s="34"/>
+      <x:c r="V6" s="34"/>
+      <x:c r="W6" s="34"/>
+      <x:c r="X6" s="34"/>
+      <x:c r="Y6" s="76"/>
+      <x:c r="Z6" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA6" s="34"/>
+      <x:c r="AB6" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC6" s="76"/>
+      <x:c r="AD6" s="34"/>
+      <x:c r="AE6" s="34"/>
+      <x:c r="AF6" s="34"/>
+      <x:c r="AG6" s="34"/>
+      <x:c r="AH6" s="34"/>
+      <x:c r="AI6" s="34"/>
+      <x:c r="AJ6" s="76"/>
+      <x:c r="AK6" s="76"/>
+      <x:c r="AL6" s="34"/>
+      <x:c r="AM6" s="34"/>
+      <x:c r="AN6" s="76"/>
+      <x:c r="AO6" s="34"/>
+      <x:c r="AP6" s="76"/>
+      <x:c r="AQ6" s="34"/>
+      <x:c r="AR6" s="76"/>
+      <x:c r="AS6" s="34"/>
+      <x:c r="AT6" s="34"/>
+      <x:c r="AU6" s="34"/>
+      <x:c r="AV6" s="34"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="95" t="str">
-        <x:v>Squirrel</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="B7" s="95" t="str">
         <x:v>Foundation</x:v>
       </x:c>
       <x:c r="C7" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="E7" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F7" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="G7" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="34"/>
+      <x:c r="F7" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" s="76"/>
       <x:c r="H7" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I7" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J7" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K7" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="L7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="M7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="N7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P7" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Q7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="R7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="S7" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T7" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="U7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="W7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Y7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV7" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A7,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I7" s="76"/>
+      <x:c r="J7" s="34"/>
+      <x:c r="K7" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L7" s="34"/>
+      <x:c r="M7" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N7" s="34"/>
+      <x:c r="O7" s="34"/>
+      <x:c r="P7" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q7" s="34"/>
+      <x:c r="R7" s="34"/>
+      <x:c r="S7" s="34"/>
+      <x:c r="T7" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U7" s="34"/>
+      <x:c r="V7" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W7" s="34"/>
+      <x:c r="X7" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y7" s="34"/>
+      <x:c r="Z7" s="34"/>
+      <x:c r="AA7" s="34"/>
+      <x:c r="AB7" s="34"/>
+      <x:c r="AC7" s="34"/>
+      <x:c r="AD7" s="34"/>
+      <x:c r="AE7" s="34"/>
+      <x:c r="AF7" s="34"/>
+      <x:c r="AG7" s="34"/>
+      <x:c r="AH7" s="34"/>
+      <x:c r="AI7" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ7" s="34"/>
+      <x:c r="AK7" s="34"/>
+      <x:c r="AL7" s="34"/>
+      <x:c r="AM7" s="34"/>
+      <x:c r="AN7" s="34"/>
+      <x:c r="AO7" s="34"/>
+      <x:c r="AP7" s="34"/>
+      <x:c r="AQ7" s="34"/>
+      <x:c r="AR7" s="34"/>
+      <x:c r="AS7" s="34"/>
+      <x:c r="AT7" s="34"/>
+      <x:c r="AU7" s="34"/>
+      <x:c r="AV7" s="34"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="95" t="str">
-        <x:v>Time</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="B8" s="95" t="str">
-        <x:v>Foundation</x:v>
-      </x:c>
-      <x:c r="C8" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>Construction</x:v>
+      </x:c>
+      <x:c r="C8" s="76"/>
       <x:c r="D8" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="F8" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="H8" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="J8" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="76"/>
+      <x:c r="F8" s="34"/>
+      <x:c r="G8" s="34"/>
+      <x:c r="H8" s="76"/>
+      <x:c r="I8" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J8" s="76"/>
       <x:c r="K8" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L8" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="M8" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N8" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="O8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="P8" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q8" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="R8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="S8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="T8" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U8" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V8" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X8" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE8" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI8" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV8" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A8,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L8" s="76"/>
+      <x:c r="M8" s="76"/>
+      <x:c r="N8" s="76"/>
+      <x:c r="O8" s="34"/>
+      <x:c r="P8" s="34"/>
+      <x:c r="Q8" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R8" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S8" s="34"/>
+      <x:c r="T8" s="34"/>
+      <x:c r="U8" s="76"/>
+      <x:c r="V8" s="34"/>
+      <x:c r="W8" s="34"/>
+      <x:c r="X8" s="34"/>
+      <x:c r="Y8" s="34"/>
+      <x:c r="Z8" s="34"/>
+      <x:c r="AA8" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB8" s="34"/>
+      <x:c r="AC8" s="34"/>
+      <x:c r="AD8" s="34"/>
+      <x:c r="AE8" s="76"/>
+      <x:c r="AF8" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG8" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH8" s="34"/>
+      <x:c r="AI8" s="34"/>
+      <x:c r="AJ8" s="34"/>
+      <x:c r="AK8" s="34"/>
+      <x:c r="AL8" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM8" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN8" s="34"/>
+      <x:c r="AO8" s="34"/>
+      <x:c r="AP8" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ8" s="34"/>
+      <x:c r="AR8" s="34"/>
+      <x:c r="AS8" s="34"/>
+      <x:c r="AT8" s="34"/>
+      <x:c r="AU8" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV8" s="34"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="95" t="str">
         <x:v>You Are Here</x:v>
       </x:c>
       <x:c r="B9" s="95" t="str">
-        <x:v>Foundation</x:v>
-      </x:c>
-      <x:c r="C9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="D9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>Construction</x:v>
+      </x:c>
+      <x:c r="C9" s="34"/>
+      <x:c r="D9" s="34"/>
       <x:c r="E9" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="76" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="I9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="34"/>
+      <x:c r="I9" s="34"/>
       <x:c r="J9" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K9" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K9" s="76"/>
       <x:c r="L9" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="N9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M9" s="34"/>
+      <x:c r="N9" s="34"/>
       <x:c r="O9" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P9" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Q9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="R9" s="76" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="S9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="T9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="U9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="W9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Y9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV9" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A9,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P9" s="76"/>
+      <x:c r="Q9" s="34"/>
+      <x:c r="R9" s="76"/>
+      <x:c r="S9" s="34"/>
+      <x:c r="T9" s="34"/>
+      <x:c r="U9" s="34"/>
+      <x:c r="V9" s="34"/>
+      <x:c r="W9" s="34"/>
+      <x:c r="X9" s="34"/>
+      <x:c r="Y9" s="34"/>
+      <x:c r="Z9" s="34"/>
+      <x:c r="AA9" s="34"/>
+      <x:c r="AB9" s="34"/>
+      <x:c r="AC9" s="34"/>
+      <x:c r="AD9" s="34"/>
+      <x:c r="AE9" s="34"/>
+      <x:c r="AF9" s="34"/>
+      <x:c r="AG9" s="34"/>
+      <x:c r="AH9" s="34"/>
+      <x:c r="AI9" s="34"/>
+      <x:c r="AJ9" s="34"/>
+      <x:c r="AK9" s="34"/>
+      <x:c r="AL9" s="34"/>
+      <x:c r="AM9" s="34"/>
+      <x:c r="AN9" s="34"/>
+      <x:c r="AO9" s="34"/>
+      <x:c r="AP9" s="34"/>
+      <x:c r="AQ9" s="34"/>
+      <x:c r="AR9" s="34"/>
+      <x:c r="AS9" s="34"/>
+      <x:c r="AT9" s="34"/>
+      <x:c r="AU9" s="34"/>
+      <x:c r="AV9" s="34"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="96" t="str">
-        <x:v>Relevance</x:v>
+        <x:v>Squirrel</x:v>
       </x:c>
       <x:c r="B10" s="96" t="str">
         <x:v>Construction</x:v>
       </x:c>
       <x:c r="C10" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="F10" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" s="78"/>
+      <x:c r="E10" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" s="78"/>
       <x:c r="G10" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="I10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="J10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="K10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="L10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="M10" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="N10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="O10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="P10" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="R10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="S10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="T10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="U10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="W10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X10" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Y10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB10" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV10" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A10,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I10" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J10" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K10" s="34"/>
+      <x:c r="L10" s="34"/>
+      <x:c r="M10" s="78"/>
+      <x:c r="N10" s="34"/>
+      <x:c r="O10" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P10" s="34"/>
+      <x:c r="Q10" s="34"/>
+      <x:c r="R10" s="34"/>
+      <x:c r="S10" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T10" s="34"/>
+      <x:c r="U10" s="34"/>
+      <x:c r="V10" s="34"/>
+      <x:c r="W10" s="34"/>
+      <x:c r="X10" s="78"/>
+      <x:c r="Y10" s="34"/>
+      <x:c r="Z10" s="34"/>
+      <x:c r="AA10" s="34"/>
+      <x:c r="AB10" s="34"/>
+      <x:c r="AC10" s="34"/>
+      <x:c r="AD10" s="34"/>
+      <x:c r="AE10" s="34"/>
+      <x:c r="AF10" s="34"/>
+      <x:c r="AG10" s="34"/>
+      <x:c r="AH10" s="34"/>
+      <x:c r="AI10" s="34"/>
+      <x:c r="AJ10" s="34"/>
+      <x:c r="AK10" s="34"/>
+      <x:c r="AL10" s="34"/>
+      <x:c r="AM10" s="34"/>
+      <x:c r="AN10" s="34"/>
+      <x:c r="AO10" s="34"/>
+      <x:c r="AP10" s="34"/>
+      <x:c r="AQ10" s="34"/>
+      <x:c r="AR10" s="34"/>
+      <x:c r="AS10" s="34"/>
+      <x:c r="AT10" s="34"/>
+      <x:c r="AU10" s="34"/>
+      <x:c r="AV10" s="34"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="96" t="str">
-        <x:v>Push</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="B11" s="96" t="str">
         <x:v>Construction</x:v>
       </x:c>
-      <x:c r="C11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="D11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="E11" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C11" s="34"/>
+      <x:c r="D11" s="34"/>
+      <x:c r="E11" s="78"/>
       <x:c r="F11" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G11" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="I11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="J11" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K11" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="L11" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="N11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="O11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="P11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Q11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="R11" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="S11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="T11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="U11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="W11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Y11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI11" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK11" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV11" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A11,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="78"/>
+      <x:c r="H11" s="34"/>
+      <x:c r="I11" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J11" s="34"/>
+      <x:c r="K11" s="78" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L11" s="34"/>
+      <x:c r="M11" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N11" s="34"/>
+      <x:c r="O11" s="34"/>
+      <x:c r="P11" s="34"/>
+      <x:c r="Q11" s="34"/>
+      <x:c r="R11" s="78" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S11" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T11" s="34"/>
+      <x:c r="U11" s="34"/>
+      <x:c r="V11" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W11" s="34"/>
+      <x:c r="X11" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y11" s="34"/>
+      <x:c r="Z11" s="34"/>
+      <x:c r="AA11" s="34"/>
+      <x:c r="AB11" s="34"/>
+      <x:c r="AC11" s="34"/>
+      <x:c r="AD11" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE11" s="34"/>
+      <x:c r="AF11" s="34"/>
+      <x:c r="AG11" s="34"/>
+      <x:c r="AH11" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI11" s="78"/>
+      <x:c r="AJ11" s="34"/>
+      <x:c r="AK11" s="34"/>
+      <x:c r="AL11" s="34"/>
+      <x:c r="AM11" s="34"/>
+      <x:c r="AN11" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO11" s="34"/>
+      <x:c r="AP11" s="34"/>
+      <x:c r="AQ11" s="34"/>
+      <x:c r="AR11" s="34"/>
+      <x:c r="AS11" s="34"/>
+      <x:c r="AT11" s="34"/>
+      <x:c r="AU11" s="34"/>
+      <x:c r="AV11" s="34"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="96" t="str">
-        <x:v>Pull</x:v>
+        <x:v>PhoneWalletKeys</x:v>
       </x:c>
       <x:c r="B12" s="96" t="str">
         <x:v>Construction</x:v>
       </x:c>
-      <x:c r="C12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
+      <x:c r="C12" s="34" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="F12" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="I12" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="K12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="L12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="M12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="N12" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="P12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Q12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="R12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="S12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="T12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="U12" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V12" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="W12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Y12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA12" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE12" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM12" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO12" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ12" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS12" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV12" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A12,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="34"/>
+      <x:c r="F12" s="78"/>
+      <x:c r="G12" s="34"/>
+      <x:c r="H12" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I12" s="78"/>
+      <x:c r="J12" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K12" s="34"/>
+      <x:c r="L12" s="34"/>
+      <x:c r="M12" s="34"/>
+      <x:c r="N12" s="34"/>
+      <x:c r="O12" s="78"/>
+      <x:c r="P12" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q12" s="34"/>
+      <x:c r="R12" s="34"/>
+      <x:c r="S12" s="34"/>
+      <x:c r="T12" s="34"/>
+      <x:c r="U12" s="34"/>
+      <x:c r="V12" s="78"/>
+      <x:c r="W12" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X12" s="34"/>
+      <x:c r="Y12" s="34"/>
+      <x:c r="Z12" s="34"/>
+      <x:c r="AA12" s="78"/>
+      <x:c r="AB12" s="34"/>
+      <x:c r="AC12" s="34"/>
+      <x:c r="AD12" s="34"/>
+      <x:c r="AE12" s="34"/>
+      <x:c r="AF12" s="34"/>
+      <x:c r="AG12" s="34"/>
+      <x:c r="AH12" s="34"/>
+      <x:c r="AI12" s="34"/>
+      <x:c r="AJ12" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK12" s="34"/>
+      <x:c r="AL12" s="34"/>
+      <x:c r="AM12" s="78"/>
+      <x:c r="AN12" s="34"/>
+      <x:c r="AO12" s="34"/>
+      <x:c r="AP12" s="34"/>
+      <x:c r="AQ12" s="78"/>
+      <x:c r="AR12" s="34"/>
+      <x:c r="AS12" s="34"/>
+      <x:c r="AT12" s="34"/>
+      <x:c r="AU12" s="34"/>
+      <x:c r="AV12" s="34"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="96" t="str">
-        <x:v>PhoneWalletKeys</x:v>
+        <x:v>Pull</x:v>
       </x:c>
       <x:c r="B13" s="96" t="str">
         <x:v>Construction</x:v>
       </x:c>
-      <x:c r="C13" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C13" s="78"/>
       <x:c r="D13" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="F13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="G13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="H13" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="J13" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K13" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="L13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="M13" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="N13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="O13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="P13" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="R13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="S13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="T13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="U13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="W13" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Y13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF13" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ13" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV13" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A13,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="34"/>
+      <x:c r="F13" s="34"/>
+      <x:c r="G13" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H13" s="78"/>
+      <x:c r="I13" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J13" s="34"/>
+      <x:c r="K13" s="78"/>
+      <x:c r="L13" s="34"/>
+      <x:c r="M13" s="78"/>
+      <x:c r="N13" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O13" s="34"/>
+      <x:c r="P13" s="34"/>
+      <x:c r="Q13" s="34"/>
+      <x:c r="R13" s="34"/>
+      <x:c r="S13" s="34"/>
+      <x:c r="T13" s="34"/>
+      <x:c r="U13" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V13" s="34"/>
+      <x:c r="W13" s="78"/>
+      <x:c r="X13" s="34"/>
+      <x:c r="Y13" s="34"/>
+      <x:c r="Z13" s="34"/>
+      <x:c r="AA13" s="34"/>
+      <x:c r="AB13" s="34"/>
+      <x:c r="AC13" s="34"/>
+      <x:c r="AD13" s="34"/>
+      <x:c r="AE13" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF13" s="78"/>
+      <x:c r="AG13" s="34"/>
+      <x:c r="AH13" s="34"/>
+      <x:c r="AI13" s="34"/>
+      <x:c r="AJ13" s="34"/>
+      <x:c r="AK13" s="34"/>
+      <x:c r="AL13" s="34"/>
+      <x:c r="AM13" s="34"/>
+      <x:c r="AN13" s="34"/>
+      <x:c r="AO13" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP13" s="34"/>
+      <x:c r="AQ13" s="34"/>
+      <x:c r="AR13" s="34"/>
+      <x:c r="AS13" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT13" s="34"/>
+      <x:c r="AU13" s="34"/>
+      <x:c r="AV13" s="34"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="96" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Weight</x:v>
       </x:c>
       <x:c r="B14" s="96" t="str">
         <x:v>Construction</x:v>
       </x:c>
-      <x:c r="C14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="D14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="E14" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
+      <x:c r="C14" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D14" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="78" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="H14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="34"/>
+      <x:c r="H14" s="34"/>
       <x:c r="I14" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J14" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="K14" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L14" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" s="78"/>
+      <x:c r="K14" s="34"/>
+      <x:c r="L14" s="78"/>
       <x:c r="M14" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="O14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="P14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Q14" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="R14" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N14" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O14" s="34"/>
+      <x:c r="P14" s="34"/>
+      <x:c r="Q14" s="78"/>
+      <x:c r="R14" s="34"/>
       <x:c r="S14" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T14" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="U14" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V14" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X14" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z14" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD14" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH14" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL14" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN14" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV14" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A14,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T14" s="78"/>
+      <x:c r="U14" s="78" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V14" s="34"/>
+      <x:c r="W14" s="34"/>
+      <x:c r="X14" s="34"/>
+      <x:c r="Y14" s="34"/>
+      <x:c r="Z14" s="78"/>
+      <x:c r="AA14" s="34"/>
+      <x:c r="AB14" s="34"/>
+      <x:c r="AC14" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD14" s="78"/>
+      <x:c r="AE14" s="34"/>
+      <x:c r="AF14" s="34"/>
+      <x:c r="AG14" s="34"/>
+      <x:c r="AH14" s="34"/>
+      <x:c r="AI14" s="34"/>
+      <x:c r="AJ14" s="34"/>
+      <x:c r="AK14" s="34"/>
+      <x:c r="AL14" s="78"/>
+      <x:c r="AM14" s="34"/>
+      <x:c r="AN14" s="34"/>
+      <x:c r="AO14" s="34"/>
+      <x:c r="AP14" s="34"/>
+      <x:c r="AQ14" s="34"/>
+      <x:c r="AR14" s="34"/>
+      <x:c r="AS14" s="34"/>
+      <x:c r="AT14" s="34"/>
+      <x:c r="AU14" s="34"/>
+      <x:c r="AV14" s="34" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="96" t="str">
-        <x:v>Weight</x:v>
+        <x:v>Push</x:v>
       </x:c>
       <x:c r="B15" s="96" t="str">
         <x:v>Construction</x:v>
       </x:c>
-      <x:c r="C15" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C15" s="78"/>
+      <x:c r="D15" s="78"/>
       <x:c r="E15" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="F15" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G15" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="H15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="I15" s="78" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J15" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="K15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="L15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="M15" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N15" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="P15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Q15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="R15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="S15" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T15" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="U15" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V15" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="W15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Y15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Z15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AA15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC15" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS15" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT15" s="78" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU15" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV15" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A15,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="78" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="34"/>
+      <x:c r="I15" s="78"/>
+      <x:c r="J15" s="78" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K15" s="34"/>
+      <x:c r="L15" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M15" s="34"/>
+      <x:c r="N15" s="34"/>
+      <x:c r="O15" s="78"/>
+      <x:c r="P15" s="34"/>
+      <x:c r="Q15" s="34"/>
+      <x:c r="R15" s="34"/>
+      <x:c r="S15" s="34"/>
+      <x:c r="T15" s="78"/>
+      <x:c r="U15" s="34"/>
+      <x:c r="V15" s="78"/>
+      <x:c r="W15" s="34"/>
+      <x:c r="X15" s="34"/>
+      <x:c r="Y15" s="34"/>
+      <x:c r="Z15" s="34"/>
+      <x:c r="AA15" s="34"/>
+      <x:c r="AB15" s="34"/>
+      <x:c r="AC15" s="34"/>
+      <x:c r="AD15" s="34"/>
+      <x:c r="AE15" s="34"/>
+      <x:c r="AF15" s="34"/>
+      <x:c r="AG15" s="34"/>
+      <x:c r="AH15" s="34"/>
+      <x:c r="AI15" s="34"/>
+      <x:c r="AJ15" s="34"/>
+      <x:c r="AK15" s="34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL15" s="34"/>
+      <x:c r="AM15" s="34"/>
+      <x:c r="AN15" s="34"/>
+      <x:c r="AO15" s="34"/>
+      <x:c r="AP15" s="34"/>
+      <x:c r="AQ15" s="34"/>
+      <x:c r="AR15" s="34"/>
+      <x:c r="AS15" s="78"/>
+      <x:c r="AT15" s="78"/>
+      <x:c r="AU15" s="34"/>
+      <x:c r="AV15" s="34"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="97" t="str">
@@ -6322,153 +5076,71 @@
         <x:v>Action</x:v>
       </x:c>
       <x:c r="C16" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D16" s="34"/>
       <x:c r="E16" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="G16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F16" s="34"/>
+      <x:c r="G16" s="34"/>
       <x:c r="H16" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="J16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="K16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" s="34"/>
+      <x:c r="J16" s="34"/>
+      <x:c r="K16" s="34"/>
       <x:c r="L16" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="N16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="O16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="P16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M16" s="34"/>
+      <x:c r="N16" s="34"/>
+      <x:c r="O16" s="34"/>
+      <x:c r="P16" s="34"/>
       <x:c r="Q16" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="S16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="T16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="U16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="V16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R16" s="34"/>
+      <x:c r="S16" s="34"/>
+      <x:c r="T16" s="34"/>
+      <x:c r="U16" s="34"/>
+      <x:c r="V16" s="34"/>
       <x:c r="W16" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X16" s="34"/>
       <x:c r="Y16" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z16" s="34"/>
       <x:c r="AA16" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AC16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AD16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB16" s="34"/>
+      <x:c r="AC16" s="34"/>
+      <x:c r="AD16" s="34"/>
+      <x:c r="AE16" s="34"/>
+      <x:c r="AF16" s="34"/>
+      <x:c r="AG16" s="34"/>
+      <x:c r="AH16" s="34"/>
+      <x:c r="AI16" s="34"/>
+      <x:c r="AJ16" s="34"/>
+      <x:c r="AK16" s="34"/>
+      <x:c r="AL16" s="34"/>
+      <x:c r="AM16" s="34"/>
+      <x:c r="AN16" s="34"/>
+      <x:c r="AO16" s="34"/>
+      <x:c r="AP16" s="34"/>
       <x:c r="AQ16" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR16" s="34"/>
+      <x:c r="AS16" s="34"/>
       <x:c r="AT16" s="34" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV16" s="34" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A16,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU16" s="34"/>
+      <x:c r="AV16" s="34"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="92" t="str">
@@ -6478,159 +5150,83 @@
         <x:v>Integration</x:v>
       </x:c>
       <x:c r="C17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,C$1)&gt;0,1,"")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,D$1)&gt;0,1,"")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,E$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,F$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F17"/>
       <x:c r="G17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,G$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,H$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H17"/>
       <x:c r="I17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,I$1)&gt;0,1,"")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,J$1)&gt;0,1,"")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,K$1)&gt;0,1,"")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="L17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,L$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,M$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M17"/>
       <x:c r="N17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,N$1)&gt;0,1,"")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="O17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,O$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,P$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P17"/>
       <x:c r="Q17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,Q$1)&gt;0,1,"")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="R17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,R$1)&gt;0,1,"")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="S17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,S$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,T$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T17"/>
       <x:c r="U17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,U$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,V$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="W17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,W$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="X17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,X$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="Y17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,Y$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V17"/>
+      <x:c r="W17"/>
+      <x:c r="X17"/>
+      <x:c r="Y17"/>
       <x:c r="Z17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,Z$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AA$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AB17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AB$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA17"/>
+      <x:c r="AB17"/>
       <x:c r="AC17" t="n">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AC$1)&gt;0,1,"")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AD$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AE17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AE$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AF17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AF$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AG17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AG$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AH17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AH$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AI17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AI$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AJ17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AJ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AK17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AK$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AL17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AL$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AM17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AM$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AN17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AN$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AO17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AO$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AP17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AP$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AQ17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AQ$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AR17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AR$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AS17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AS$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AT17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AT$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AU17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AU$1)&gt;0,1,"")</x:f>
-      </x:c>
-      <x:c r="AV17" t="str">
-        <x:f>IF(COUNTIFS(Connections!$B:$B,$A17,Connections!$C:$C,AV$1)&gt;0,1,"")</x:f>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD17"/>
+      <x:c r="AE17"/>
+      <x:c r="AF17"/>
+      <x:c r="AG17"/>
+      <x:c r="AH17"/>
+      <x:c r="AI17"/>
+      <x:c r="AJ17"/>
+      <x:c r="AK17"/>
+      <x:c r="AL17"/>
+      <x:c r="AM17"/>
+      <x:c r="AN17"/>
+      <x:c r="AO17"/>
+      <x:c r="AP17"/>
+      <x:c r="AQ17"/>
+      <x:c r="AR17"/>
+      <x:c r="AS17"/>
+      <x:c r="AT17"/>
+      <x:c r="AU17"/>
+      <x:c r="AV17"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6688,17 +5284,16 @@
         <x:v>Basal ganglia / striatum</x:v>
       </x:c>
       <x:c r="B2" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A2)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D2" s="34" t="str">
-        <x:v>EndGame, How Long Is a Thought?, Squirrel, Time</x:v>
+        <x:v>Relevance, EndGame, How Long Is a Thought?, Time</x:v>
       </x:c>
       <x:c r="E2" s="34" t="str">
-        <x:v>Relevance, PhoneWalletKeys, Weight</x:v>
+        <x:v>Squirrel, PhoneWalletKeys, Weight</x:v>
       </x:c>
       <x:c r="F2" s="34" t="str">
         <x:v>WhatchyaDoin</x:v>
@@ -6719,19 +5314,18 @@
         <x:v>Hippocampus / medial temporal lobe</x:v>
       </x:c>
       <x:c r="B3" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A3)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D3" s="34" t="str">
-        <x:v>How Long Is a Thought?, Icarus, Time</x:v>
+        <x:v>Relevance, How Long Is a Thought?, Time</x:v>
       </x:c>
       <x:c r="E3" s="34" t="str">
-        <x:v>Relevance, Pull, PhoneWalletKeys, Weight</x:v>
-      </x:c>
-      <x:c r="F3" s="34" t="str"/>
+        <x:v>Icarus, PhoneWalletKeys, Pull, Weight</x:v>
+      </x:c>
+      <x:c r="F3" s="34"/>
       <x:c r="G3" s="34" t="str">
         <x:v>FutureYou</x:v>
       </x:c>
@@ -6748,17 +5342,16 @@
         <x:v>dACC / midcingulate cortex</x:v>
       </x:c>
       <x:c r="B4" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A4)</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D4" s="34" t="str">
-        <x:v>Containment, Squirrel, You Are Here</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="E4" s="34" t="str">
-        <x:v>Push, Weight</x:v>
+        <x:v>You Are Here, Squirrel, Weight, Push</x:v>
       </x:c>
       <x:c r="F4" s="34" t="str">
         <x:v>WhatchyaDoin</x:v>
@@ -6779,20 +5372,19 @@
         <x:v>Anterior insula</x:v>
       </x:c>
       <x:c r="B5" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A5)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D5" s="34" t="str">
-        <x:v>Containment, Time, You Are Here</x:v>
+        <x:v>Containment, Time</x:v>
       </x:c>
       <x:c r="E5" s="34" t="str">
-        <x:v>Push, FuckYourFeelings, Weight</x:v>
-      </x:c>
-      <x:c r="F5" s="34" t="str"/>
-      <x:c r="G5" s="34" t="str"/>
+        <x:v>You Are Here, FuckYourFeelings, Weight, Push</x:v>
+      </x:c>
+      <x:c r="F5" s="34"/>
+      <x:c r="G5" s="34"/>
       <x:c r="H5" s="34"/>
       <x:c r="I5" s="34" t="str">
         <x:v>Anterior insula</x:v>
@@ -6806,19 +5398,18 @@
         <x:v>aPFC / frontopolar cortex</x:v>
       </x:c>
       <x:c r="B6" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A6)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C6" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D6" s="34" t="str">
-        <x:v>Squirrel, You Are Here</x:v>
+        <x:v>Relevance</x:v>
       </x:c>
       <x:c r="E6" s="34" t="str">
-        <x:v>Relevance, Push, Pull</x:v>
-      </x:c>
-      <x:c r="F6" s="34" t="str"/>
+        <x:v>You Are Here, Squirrel, Pull, Push</x:v>
+      </x:c>
+      <x:c r="F6" s="34"/>
       <x:c r="G6" s="34" t="str">
         <x:v>FutureYou</x:v>
       </x:c>
@@ -6835,22 +5426,21 @@
         <x:v>SMA / pre-SMA</x:v>
       </x:c>
       <x:c r="B7" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A7)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D7" s="34" t="str">
-        <x:v>EndGame, How Long Is a Thought?, Squirrel, Time</x:v>
+        <x:v>EndGame, How Long Is a Thought?, Time</x:v>
       </x:c>
       <x:c r="E7" s="34" t="str">
-        <x:v>PhoneWalletKeys</x:v>
+        <x:v>Squirrel, PhoneWalletKeys</x:v>
       </x:c>
       <x:c r="F7" s="34" t="str">
         <x:v>WhatchyaDoin</x:v>
       </x:c>
-      <x:c r="G7" s="34" t="str"/>
+      <x:c r="G7" s="34"/>
       <x:c r="H7" s="34"/>
       <x:c r="I7" s="34" t="str">
         <x:v>SMA / pre-SMA</x:v>
@@ -6864,19 +5454,16 @@
         <x:v>Valuation systems</x:v>
       </x:c>
       <x:c r="B8" s="69" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A8)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C8" s="69" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="D8" s="34" t="str">
-        <x:v>Icarus, Squirrel</x:v>
-      </x:c>
+      <x:c r="D8" s="34"/>
       <x:c r="E8" s="34" t="str">
-        <x:v>Pull, FuckYourFeelings, Weight</x:v>
-      </x:c>
-      <x:c r="F8" s="34" t="str"/>
+        <x:v>Icarus, Squirrel, FuckYourFeelings, Pull, Weight</x:v>
+      </x:c>
+      <x:c r="F8" s="34"/>
       <x:c r="G8" s="34" t="str">
         <x:v>FutureYou</x:v>
       </x:c>
@@ -6893,19 +5480,16 @@
         <x:v>DLPFC</x:v>
       </x:c>
       <x:c r="B9" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A9)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="C9" s="70" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="D9" s="34" t="str">
-        <x:v>Squirrel, You Are Here</x:v>
-      </x:c>
+      <x:c r="D9" s="34"/>
       <x:c r="E9" s="34" t="str">
-        <x:v>Push, PhoneWalletKeys</x:v>
-      </x:c>
-      <x:c r="F9" s="34" t="str"/>
+        <x:v>You Are Here, Squirrel, PhoneWalletKeys, Push</x:v>
+      </x:c>
+      <x:c r="F9" s="34"/>
       <x:c r="G9" s="34" t="str">
         <x:v>FutureYou</x:v>
       </x:c>
@@ -6922,19 +5506,18 @@
         <x:v>Interoceptive systems</x:v>
       </x:c>
       <x:c r="B10" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A10)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="C10" s="70" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D10" s="34" t="str">
-        <x:v>Containment, Icarus, Time</x:v>
+        <x:v>Containment, Time</x:v>
       </x:c>
       <x:c r="E10" s="34" t="str">
-        <x:v>FuckYourFeelings</x:v>
-      </x:c>
-      <x:c r="F10" s="34" t="str"/>
+        <x:v>Icarus, FuckYourFeelings</x:v>
+      </x:c>
+      <x:c r="F10" s="34"/>
       <x:c r="G10" s="34" t="str">
         <x:v>FutureYou</x:v>
       </x:c>
@@ -6951,17 +5534,16 @@
         <x:v>Posterior parietal cortex</x:v>
       </x:c>
       <x:c r="B11" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A11)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="C11" s="70" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="D11" s="34" t="str">
-        <x:v>EndGame, You Are Here</x:v>
+        <x:v>EndGame</x:v>
       </x:c>
       <x:c r="E11" s="34" t="str">
-        <x:v>Push</x:v>
+        <x:v>You Are Here, Push</x:v>
       </x:c>
       <x:c r="F11" s="34" t="str">
         <x:v>WhatchyaDoin</x:v>
@@ -6982,7 +5564,6 @@
         <x:v>Autonomic / arousal systems</x:v>
       </x:c>
       <x:c r="B12" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A12)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C12" s="70" t="str">
@@ -6994,8 +5575,8 @@
       <x:c r="E12" s="34" t="str">
         <x:v>FuckYourFeelings, Weight</x:v>
       </x:c>
-      <x:c r="F12" s="34" t="str"/>
-      <x:c r="G12" s="34" t="str"/>
+      <x:c r="F12" s="34"/>
+      <x:c r="G12" s="34"/>
       <x:c r="H12" s="34"/>
       <x:c r="I12" s="34" t="str">
         <x:v>Autonomic / arousal systems</x:v>
@@ -7009,7 +5590,6 @@
         <x:v>Default mode network</x:v>
       </x:c>
       <x:c r="B13" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A13)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C13" s="70" t="str">
@@ -7021,7 +5601,7 @@
       <x:c r="E13" s="34" t="str">
         <x:v>Pull, Weight</x:v>
       </x:c>
-      <x:c r="F13" s="34" t="str"/>
+      <x:c r="F13" s="34"/>
       <x:c r="G13" s="34" t="str">
         <x:v>FutureYou</x:v>
       </x:c>
@@ -7038,17 +5618,18 @@
         <x:v>Frontoparietal control network</x:v>
       </x:c>
       <x:c r="B14" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A14)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C14" s="70" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D14" s="34" t="str">
-        <x:v>Containment, Squirrel, You Are Here</x:v>
-      </x:c>
-      <x:c r="E14" s="34" t="str"/>
-      <x:c r="F14" s="34" t="str"/>
+        <x:v>Containment</x:v>
+      </x:c>
+      <x:c r="E14" s="34" t="str">
+        <x:v>You Are Here, Squirrel</x:v>
+      </x:c>
+      <x:c r="F14" s="34"/>
       <x:c r="G14" s="34" t="str">
         <x:v>FutureYou</x:v>
       </x:c>
@@ -7065,20 +5646,19 @@
         <x:v>Prefrontal cortex, general</x:v>
       </x:c>
       <x:c r="B15" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A15)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C15" s="70" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D15" s="34" t="str">
-        <x:v>How Long Is a Thought?, Time</x:v>
+        <x:v>Relevance, How Long Is a Thought?, Time</x:v>
       </x:c>
       <x:c r="E15" s="34" t="str">
-        <x:v>Relevance, PhoneWalletKeys</x:v>
-      </x:c>
-      <x:c r="F15" s="34" t="str"/>
-      <x:c r="G15" s="34" t="str"/>
+        <x:v>PhoneWalletKeys</x:v>
+      </x:c>
+      <x:c r="F15" s="34"/>
+      <x:c r="G15" s="34"/>
       <x:c r="H15" s="34"/>
       <x:c r="I15" s="34" t="str">
         <x:v>Prefrontal cortex, general</x:v>
@@ -7092,16 +5672,17 @@
         <x:v>Sensory cortex / sensory systems</x:v>
       </x:c>
       <x:c r="B16" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A16)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C16" s="70" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D16" s="34" t="str">
-        <x:v>Containment, Icarus</x:v>
-      </x:c>
-      <x:c r="E16" s="34" t="str"/>
+        <x:v>Containment</x:v>
+      </x:c>
+      <x:c r="E16" s="34" t="str">
+        <x:v>Icarus</x:v>
+      </x:c>
       <x:c r="F16" s="34" t="str">
         <x:v>WhatchyaDoin</x:v>
       </x:c>
@@ -7121,19 +5702,18 @@
         <x:v>Thalamus</x:v>
       </x:c>
       <x:c r="B17" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A17)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C17" s="70" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D17" s="34" t="str">
-        <x:v>Containment, Icarus</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="E17" s="34" t="str">
-        <x:v>FuckYourFeelings</x:v>
-      </x:c>
-      <x:c r="F17" s="34" t="str"/>
+        <x:v>Icarus, FuckYourFeelings</x:v>
+      </x:c>
+      <x:c r="F17" s="34"/>
       <x:c r="G17" s="34" t="str">
         <x:v>FutureYou</x:v>
       </x:c>
@@ -7146,19 +5726,16 @@
         <x:v>vmPFC / OFC</x:v>
       </x:c>
       <x:c r="B18" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A18)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="C18" s="70" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D18" s="34" t="str">
-        <x:v>Squirrel</x:v>
-      </x:c>
+      <x:c r="D18" s="34"/>
       <x:c r="E18" s="34" t="str">
-        <x:v>FuckYourFeelings, Weight</x:v>
-      </x:c>
-      <x:c r="F18" s="34" t="str"/>
+        <x:v>Squirrel, FuckYourFeelings, Weight</x:v>
+      </x:c>
+      <x:c r="F18" s="34"/>
       <x:c r="G18" s="34" t="str">
         <x:v>FutureYou</x:v>
       </x:c>
@@ -7171,7 +5748,6 @@
         <x:v>Cerebellum</x:v>
       </x:c>
       <x:c r="B19" s="70" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A19)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C19" s="70" t="str">
@@ -7180,9 +5756,9 @@
       <x:c r="D19" s="34" t="str">
         <x:v>EndGame, How Long Is a Thought?, Time</x:v>
       </x:c>
-      <x:c r="E19" s="34" t="str"/>
-      <x:c r="F19" s="34" t="str"/>
-      <x:c r="G19" s="34" t="str"/>
+      <x:c r="E19" s="34"/>
+      <x:c r="F19" s="34"/>
+      <x:c r="G19" s="34"/>
       <x:c r="H19" s="34"/>
       <x:c r="I19" s="34"/>
       <x:c r="J19" s="34"/>
@@ -7192,17 +5768,16 @@
         <x:v>Medial prefrontal cortex</x:v>
       </x:c>
       <x:c r="B20" s="71" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A20)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C20" s="71" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D20" s="34" t="str"/>
+      <x:c r="D20" s="34"/>
       <x:c r="E20" s="34" t="str">
         <x:v>Pull, Weight</x:v>
       </x:c>
-      <x:c r="F20" s="34" t="str"/>
+      <x:c r="F20" s="34"/>
       <x:c r="G20" s="34" t="str">
         <x:v>FutureYou</x:v>
       </x:c>
@@ -7215,7 +5790,6 @@
         <x:v>Posterior / mid insula</x:v>
       </x:c>
       <x:c r="B21" s="71" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A21)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C21" s="71" t="str">
@@ -7227,8 +5801,8 @@
       <x:c r="E21" s="34" t="str">
         <x:v>FuckYourFeelings</x:v>
       </x:c>
-      <x:c r="F21" s="34" t="str"/>
-      <x:c r="G21" s="34" t="str"/>
+      <x:c r="F21" s="34"/>
+      <x:c r="G21" s="34"/>
       <x:c r="H21" s="34"/>
       <x:c r="I21" s="34"/>
       <x:c r="J21" s="34"/>
@@ -7238,7 +5812,6 @@
         <x:v>Premotor cortex</x:v>
       </x:c>
       <x:c r="B22" s="71" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A22)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C22" s="71" t="str">
@@ -7253,7 +5826,7 @@
       <x:c r="F22" s="34" t="str">
         <x:v>WhatchyaDoin</x:v>
       </x:c>
-      <x:c r="G22" s="34" t="str"/>
+      <x:c r="G22" s="34"/>
       <x:c r="H22" s="34"/>
       <x:c r="I22" s="34"/>
       <x:c r="J22" s="34"/>
@@ -7263,7 +5836,6 @@
         <x:v>ACC</x:v>
       </x:c>
       <x:c r="B23" s="71" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A23)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C23" s="71" t="str">
@@ -7275,8 +5847,8 @@
       <x:c r="E23" s="34" t="str">
         <x:v>FuckYourFeelings</x:v>
       </x:c>
-      <x:c r="F23" s="34" t="str"/>
-      <x:c r="G23" s="34" t="str"/>
+      <x:c r="F23" s="34"/>
+      <x:c r="G23" s="34"/>
       <x:c r="H23" s="34"/>
       <x:c r="I23" s="34"/>
       <x:c r="J23" s="34"/>
@@ -7286,7 +5858,6 @@
         <x:v>Dorsal premotor cortex</x:v>
       </x:c>
       <x:c r="B24" s="71" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A24)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C24" s="71" t="str">
@@ -7295,11 +5866,11 @@
       <x:c r="D24" s="34" t="str">
         <x:v>EndGame</x:v>
       </x:c>
-      <x:c r="E24" s="34" t="str"/>
+      <x:c r="E24" s="34"/>
       <x:c r="F24" s="34" t="str">
         <x:v>WhatchyaDoin</x:v>
       </x:c>
-      <x:c r="G24" s="34" t="str"/>
+      <x:c r="G24" s="34"/>
       <x:c r="H24" s="34"/>
       <x:c r="I24" s="34"/>
       <x:c r="J24" s="34"/>
@@ -7309,7 +5880,6 @@
         <x:v>Frontoparietal attention network</x:v>
       </x:c>
       <x:c r="B25" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A25)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C25" s="72" t="str">
@@ -7318,8 +5888,8 @@
       <x:c r="D25" s="34" t="str">
         <x:v>How Long Is a Thought?</x:v>
       </x:c>
-      <x:c r="E25" s="34" t="str"/>
-      <x:c r="F25" s="34" t="str"/>
+      <x:c r="E25" s="34"/>
+      <x:c r="F25" s="34"/>
       <x:c r="G25" s="34" t="str">
         <x:v>FutureYou</x:v>
       </x:c>
@@ -7332,20 +5902,19 @@
         <x:v>Neuromodulatory systems</x:v>
       </x:c>
       <x:c r="B26" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A26)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C26" s="72" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="D26" s="34" t="str">
+      <x:c r="D26" s="34"/>
+      <x:c r="E26" s="34" t="str">
         <x:v>Icarus</x:v>
       </x:c>
-      <x:c r="E26" s="34" t="str"/>
       <x:c r="F26" s="34" t="str">
         <x:v>WhatchyaDoin</x:v>
       </x:c>
-      <x:c r="G26" s="34" t="str"/>
+      <x:c r="G26" s="34"/>
       <x:c r="H26" s="34"/>
       <x:c r="I26" s="34"/>
       <x:c r="J26" s="34"/>
@@ -7355,20 +5924,17 @@
         <x:v>Prospective-memory / timing systems</x:v>
       </x:c>
       <x:c r="B27" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A27)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C27" s="72" t="str">
         <x:v>Low</x:v>
       </x:c>
       <x:c r="D27" s="34" t="str">
-        <x:v>How Long Is a Thought?</x:v>
-      </x:c>
-      <x:c r="E27" s="34" t="str">
-        <x:v>Relevance</x:v>
-      </x:c>
-      <x:c r="F27" s="34" t="str"/>
-      <x:c r="G27" s="34" t="str"/>
+        <x:v>Relevance, How Long Is a Thought?</x:v>
+      </x:c>
+      <x:c r="E27" s="34"/>
+      <x:c r="F27" s="34"/>
+      <x:c r="G27" s="34"/>
       <x:c r="H27" s="34"/>
       <x:c r="I27" s="34"/>
       <x:c r="J27" s="34"/>
@@ -7378,17 +5944,16 @@
         <x:v>TPJ / pSTS</x:v>
       </x:c>
       <x:c r="B28" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A28)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C28" s="72" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="D28" s="34" t="str"/>
+      <x:c r="D28" s="34"/>
       <x:c r="E28" s="34" t="str">
         <x:v>Weight</x:v>
       </x:c>
-      <x:c r="F28" s="34" t="str"/>
+      <x:c r="F28" s="34"/>
       <x:c r="G28" s="34" t="str">
         <x:v>FutureYou</x:v>
       </x:c>
@@ -7401,18 +5966,17 @@
         <x:v>Amygdala</x:v>
       </x:c>
       <x:c r="B29" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A29)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C29" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D29" s="34" t="str"/>
+      <x:c r="D29" s="34"/>
       <x:c r="E29" s="34" t="str">
         <x:v>FuckYourFeelings</x:v>
       </x:c>
-      <x:c r="F29" s="34" t="str"/>
-      <x:c r="G29" s="34" t="str"/>
+      <x:c r="F29" s="34"/>
+      <x:c r="G29" s="34"/>
       <x:c r="H29" s="34"/>
       <x:c r="I29" s="34"/>
       <x:c r="J29" s="34"/>
@@ -7422,18 +5986,17 @@
         <x:v>Angular gyrus</x:v>
       </x:c>
       <x:c r="B30" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A30)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D30" s="34" t="str"/>
+      <x:c r="D30" s="34"/>
       <x:c r="E30" s="34" t="str">
         <x:v>Pull</x:v>
       </x:c>
-      <x:c r="F30" s="34" t="str"/>
-      <x:c r="G30" s="34" t="str"/>
+      <x:c r="F30" s="34"/>
+      <x:c r="G30" s="34"/>
       <x:c r="H30" s="34"/>
       <x:c r="I30" s="34"/>
       <x:c r="J30" s="34"/>
@@ -7443,18 +6006,17 @@
         <x:v>Apical dendrites</x:v>
       </x:c>
       <x:c r="B31" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A31)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C31" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D31" s="34" t="str">
+      <x:c r="D31" s="34"/>
+      <x:c r="E31" s="34" t="str">
         <x:v>Icarus</x:v>
       </x:c>
-      <x:c r="E31" s="34" t="str"/>
-      <x:c r="F31" s="34" t="str"/>
-      <x:c r="G31" s="34" t="str"/>
+      <x:c r="F31" s="34"/>
+      <x:c r="G31" s="34"/>
       <x:c r="H31" s="34"/>
       <x:c r="I31" s="34"/>
       <x:c r="J31" s="34"/>
@@ -7464,18 +6026,17 @@
         <x:v>Association cortex</x:v>
       </x:c>
       <x:c r="B32" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A32)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C32" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D32" s="34" t="str">
+      <x:c r="D32" s="34"/>
+      <x:c r="E32" s="34" t="str">
         <x:v>Icarus</x:v>
       </x:c>
-      <x:c r="E32" s="34" t="str"/>
-      <x:c r="F32" s="34" t="str"/>
-      <x:c r="G32" s="34" t="str"/>
+      <x:c r="F32" s="34"/>
+      <x:c r="G32" s="34"/>
       <x:c r="H32" s="34"/>
       <x:c r="I32" s="34"/>
       <x:c r="J32" s="34"/>
@@ -7485,18 +6046,17 @@
         <x:v>Brainstem</x:v>
       </x:c>
       <x:c r="B33" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A33)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C33" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D33" s="34" t="str"/>
+      <x:c r="D33" s="34"/>
       <x:c r="E33" s="34" t="str">
         <x:v>FuckYourFeelings</x:v>
       </x:c>
-      <x:c r="F33" s="34" t="str"/>
-      <x:c r="G33" s="34" t="str"/>
+      <x:c r="F33" s="34"/>
+      <x:c r="G33" s="34"/>
       <x:c r="H33" s="34"/>
       <x:c r="I33" s="34"/>
       <x:c r="J33" s="34"/>
@@ -7506,7 +6066,6 @@
         <x:v>Cardiac systems</x:v>
       </x:c>
       <x:c r="B34" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A34)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C34" s="72" t="str">
@@ -7515,9 +6074,9 @@
       <x:c r="D34" s="34" t="str">
         <x:v>Time</x:v>
       </x:c>
-      <x:c r="E34" s="34" t="str"/>
-      <x:c r="F34" s="34" t="str"/>
-      <x:c r="G34" s="34" t="str"/>
+      <x:c r="E34" s="34"/>
+      <x:c r="F34" s="34"/>
+      <x:c r="G34" s="34"/>
       <x:c r="H34" s="34"/>
       <x:c r="I34" s="34"/>
       <x:c r="J34" s="34"/>
@@ -7527,18 +6086,17 @@
         <x:v>Caudate</x:v>
       </x:c>
       <x:c r="B35" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A35)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C35" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D35" s="34" t="str"/>
+      <x:c r="D35" s="34"/>
       <x:c r="E35" s="34" t="str">
         <x:v>PhoneWalletKeys</x:v>
       </x:c>
-      <x:c r="F35" s="34" t="str"/>
-      <x:c r="G35" s="34" t="str"/>
+      <x:c r="F35" s="34"/>
+      <x:c r="G35" s="34"/>
       <x:c r="H35" s="34"/>
       <x:c r="I35" s="34"/>
       <x:c r="J35" s="34"/>
@@ -7548,18 +6106,17 @@
         <x:v>Frontostriatal systems</x:v>
       </x:c>
       <x:c r="B36" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A36)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C36" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D36" s="34" t="str"/>
+      <x:c r="D36" s="34"/>
       <x:c r="E36" s="34" t="str">
         <x:v>Push</x:v>
       </x:c>
-      <x:c r="F36" s="34" t="str"/>
-      <x:c r="G36" s="34" t="str"/>
+      <x:c r="F36" s="34"/>
+      <x:c r="G36" s="34"/>
       <x:c r="H36" s="34"/>
       <x:c r="I36" s="34"/>
       <x:c r="J36" s="34"/>
@@ -7569,18 +6126,17 @@
         <x:v>Gene-regulatory / plasticity systems</x:v>
       </x:c>
       <x:c r="B37" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A37)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C37" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D37" s="34" t="str">
+      <x:c r="D37" s="34"/>
+      <x:c r="E37" s="34" t="str">
         <x:v>Icarus</x:v>
       </x:c>
-      <x:c r="E37" s="34" t="str"/>
-      <x:c r="F37" s="34" t="str"/>
-      <x:c r="G37" s="34" t="str"/>
+      <x:c r="F37" s="34"/>
+      <x:c r="G37" s="34"/>
       <x:c r="H37" s="34"/>
       <x:c r="I37" s="34"/>
       <x:c r="J37" s="34"/>
@@ -7590,18 +6146,17 @@
         <x:v>Higher-order thalamus</x:v>
       </x:c>
       <x:c r="B38" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A38)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C38" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D38" s="34" t="str">
+      <x:c r="D38" s="34"/>
+      <x:c r="E38" s="34" t="str">
         <x:v>Icarus</x:v>
       </x:c>
-      <x:c r="E38" s="34" t="str"/>
-      <x:c r="F38" s="34" t="str"/>
-      <x:c r="G38" s="34" t="str"/>
+      <x:c r="F38" s="34"/>
+      <x:c r="G38" s="34"/>
       <x:c r="H38" s="34"/>
       <x:c r="I38" s="34"/>
       <x:c r="J38" s="34"/>
@@ -7611,18 +6166,17 @@
         <x:v>Hypothalamus</x:v>
       </x:c>
       <x:c r="B39" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A39)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C39" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D39" s="34" t="str"/>
+      <x:c r="D39" s="34"/>
       <x:c r="E39" s="34" t="str">
         <x:v>FuckYourFeelings</x:v>
       </x:c>
-      <x:c r="F39" s="34" t="str"/>
-      <x:c r="G39" s="34" t="str"/>
+      <x:c r="F39" s="34"/>
+      <x:c r="G39" s="34"/>
       <x:c r="H39" s="34"/>
       <x:c r="I39" s="34"/>
       <x:c r="J39" s="34"/>
@@ -7632,18 +6186,17 @@
         <x:v>Lateral / anterior prefrontal cortex</x:v>
       </x:c>
       <x:c r="B40" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A40)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C40" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D40" s="34" t="str"/>
+      <x:c r="D40" s="34"/>
       <x:c r="E40" s="34" t="str">
         <x:v>Pull</x:v>
       </x:c>
-      <x:c r="F40" s="34" t="str"/>
-      <x:c r="G40" s="34" t="str"/>
+      <x:c r="F40" s="34"/>
+      <x:c r="G40" s="34"/>
       <x:c r="H40" s="34"/>
       <x:c r="I40" s="34"/>
       <x:c r="J40" s="34"/>
@@ -7653,18 +6206,17 @@
         <x:v>Layer-5 pyramidal neurons</x:v>
       </x:c>
       <x:c r="B41" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A41)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C41" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D41" s="34" t="str">
+      <x:c r="D41" s="34"/>
+      <x:c r="E41" s="34" t="str">
         <x:v>Icarus</x:v>
       </x:c>
-      <x:c r="E41" s="34" t="str"/>
-      <x:c r="F41" s="34" t="str"/>
-      <x:c r="G41" s="34" t="str"/>
+      <x:c r="F41" s="34"/>
+      <x:c r="G41" s="34"/>
       <x:c r="H41" s="34"/>
       <x:c r="I41" s="34"/>
       <x:c r="J41" s="34"/>
@@ -7674,18 +6226,17 @@
         <x:v>Locus coeruleus / noradrenergic system</x:v>
       </x:c>
       <x:c r="B42" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A42)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C42" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D42" s="34" t="str"/>
-      <x:c r="E42" s="34" t="str"/>
+      <x:c r="D42" s="34"/>
+      <x:c r="E42" s="34"/>
       <x:c r="F42" s="34" t="str">
         <x:v>WhatchyaDoin</x:v>
       </x:c>
-      <x:c r="G42" s="34" t="str"/>
+      <x:c r="G42" s="34"/>
       <x:c r="H42" s="34"/>
       <x:c r="I42" s="34"/>
       <x:c r="J42" s="34"/>
@@ -7695,7 +6246,6 @@
         <x:v>Motor cortex</x:v>
       </x:c>
       <x:c r="B43" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A43)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C43" s="72" t="str">
@@ -7704,9 +6254,9 @@
       <x:c r="D43" s="34" t="str">
         <x:v>EndGame</x:v>
       </x:c>
-      <x:c r="E43" s="34" t="str"/>
-      <x:c r="F43" s="34" t="str"/>
-      <x:c r="G43" s="34" t="str"/>
+      <x:c r="E43" s="34"/>
+      <x:c r="F43" s="34"/>
+      <x:c r="G43" s="34"/>
       <x:c r="H43" s="34"/>
       <x:c r="I43" s="34"/>
       <x:c r="J43" s="34"/>
@@ -7716,18 +6266,17 @@
         <x:v>PCC / precuneus</x:v>
       </x:c>
       <x:c r="B44" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A44)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C44" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D44" s="34" t="str"/>
+      <x:c r="D44" s="34"/>
       <x:c r="E44" s="34" t="str">
         <x:v>Pull</x:v>
       </x:c>
-      <x:c r="F44" s="34" t="str"/>
-      <x:c r="G44" s="34" t="str"/>
+      <x:c r="F44" s="34"/>
+      <x:c r="G44" s="34"/>
       <x:c r="H44" s="34"/>
       <x:c r="I44" s="34"/>
       <x:c r="J44" s="34"/>
@@ -7737,18 +6286,17 @@
         <x:v>Substantia nigra dopaminergic system</x:v>
       </x:c>
       <x:c r="B45" s="72" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A45)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C45" s="72" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D45" s="34" t="str"/>
-      <x:c r="E45" s="34" t="str"/>
+      <x:c r="D45" s="34"/>
+      <x:c r="E45" s="34"/>
       <x:c r="F45" s="34" t="str">
         <x:v>WhatchyaDoin</x:v>
       </x:c>
-      <x:c r="G45" s="34" t="str"/>
+      <x:c r="G45" s="34"/>
       <x:c r="H45" s="34"/>
       <x:c r="I45" s="34"/>
       <x:c r="J45" s="34"/>
@@ -7758,18 +6306,17 @@
         <x:v>Thalamocortical circuits</x:v>
       </x:c>
       <x:c r="B46" s="34" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A46)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C46" s="34" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D46" s="34" t="str">
+      <x:c r="D46" s="34"/>
+      <x:c r="E46" s="34" t="str">
         <x:v>Icarus</x:v>
       </x:c>
-      <x:c r="E46" s="34" t="str"/>
-      <x:c r="F46" s="34" t="str"/>
-      <x:c r="G46" s="34" t="str"/>
+      <x:c r="F46" s="34"/>
+      <x:c r="G46" s="34"/>
       <x:c r="H46" s="34"/>
       <x:c r="I46" s="34"/>
       <x:c r="J46" s="34"/>
@@ -7779,27 +6326,26 @@
         <x:v>Ventral striatum</x:v>
       </x:c>
       <x:c r="B47" s="34" t="n">
-        <x:f>COUNTIF(Connections!$C:$C,A47)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C47" s="34" t="str">
         <x:v>Singleton</x:v>
       </x:c>
-      <x:c r="D47" s="34" t="str"/>
+      <x:c r="D47" s="34"/>
       <x:c r="E47" s="34" t="str">
         <x:v>Weight</x:v>
       </x:c>
-      <x:c r="F47" s="34" t="str"/>
-      <x:c r="G47" s="34" t="str"/>
+      <x:c r="F47" s="34"/>
+      <x:c r="G47" s="34"/>
       <x:c r="H47" s="34"/>
       <x:c r="I47" s="34"/>
       <x:c r="J47" s="34"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R975a3f8d4c714055"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a90aa2cc2574ca2"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd22a0d01e1114303"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c9894ede3094b44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7883,10 +6429,10 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" t="str">
-        <x:v>Containment</x:v>
+        <x:v>Relevance</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>Just because you felt it, did it matter?</x:v>
+        <x:v>You know it. But does it matter right now?</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
@@ -7899,34 +6445,34 @@
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
       <x:c r="A5" t="str">
-        <x:v>How Long Is a Thought?</x:v>
+        <x:v>Containment</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>How long was that thought—for you, or for me?</x:v>
+        <x:v>Just because you felt it, did it matter?</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
       <x:c r="A6" t="str">
-        <x:v>Icarus</x:v>
+        <x:v>How Long Is a Thought?</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>Is your past still controlling you, or merely explaining you?</x:v>
+        <x:v>How long was that thought—for you, or for me?</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
       <x:c r="A7" t="str">
-        <x:v>Squirrel</x:v>
+        <x:v>Time</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>You wanted to do it. So why didn’t you?</x:v>
+        <x:v>Knowing the clock is not obeying the clock.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
       <x:c r="A8" t="str">
-        <x:v>Time</x:v>
+        <x:v>Icarus</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>Knowing the clock is not obeying the clock.</x:v>
+        <x:v>Is your past still controlling you, or merely explaining you?</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="25" customHeight="1">
@@ -7939,50 +6485,50 @@
     </x:row>
     <x:row r="10" ht="25" customHeight="1">
       <x:c r="A10" t="str">
-        <x:v>Relevance</x:v>
+        <x:v>Squirrel</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>You know it. But does it matter right now?</x:v>
+        <x:v>You wanted to do it. So why didn’t you?</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">
       <x:c r="A11" t="str">
-        <x:v>Push</x:v>
+        <x:v>FuckYourFeelings</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>Were you incapable, or did the world change underneath you?</x:v>
+        <x:v>Your feelings are real. Maybe?</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="25" customHeight="1">
       <x:c r="A12" t="str">
-        <x:v>Pull</x:v>
+        <x:v>PhoneWalletKeys</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>Did you solve the problem or finally see the other one?</x:v>
+        <x:v>Are you choosing something new, or forgetting what’s old?</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="25" customHeight="1">
       <x:c r="A13" t="str">
-        <x:v>PhoneWalletKeys</x:v>
+        <x:v>Pull</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>Are you choosing something new, or forgetting what’s old?</x:v>
+        <x:v>Did you solve the problem or finally see the other one?</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="25" customHeight="1">
       <x:c r="A14" t="str">
-        <x:v>FuckYourFeelings</x:v>
+        <x:v>Weight</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>Your feelings are real. Maybe?</x:v>
+        <x:v>You understand the words. But do they mean anything to you?</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="25" customHeight="1">
       <x:c r="A15" t="str">
-        <x:v>Weight</x:v>
+        <x:v>Push</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>You understand the words. But do they mean anything to you?</x:v>
+        <x:v>Were you incapable, or did the world change underneath you?</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="25" customHeight="1">
@@ -7998,7 +6544,7 @@
         <x:v>FutureYou</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>Manuscript summary pending.</x:v>
+        <x:v>How does what feels possible today shape what you encounter next?</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
